--- a/Treinamento/erro/PendenciaGOInspecao.xlsx
+++ b/Treinamento/erro/PendenciaGOInspecao.xlsx
@@ -1,28 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr codeName="EstaPastaDeTrabalho"/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\erro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{00C233CD-0D04-41CD-A247-8A040C744602}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3FCE921-E017-4BBB-959B-7E1692664C2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="11385" windowWidth="21600" xWindow="26640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}" yWindow="1725"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="envioPendenciaGOInspecao" r:id="rId1" sheetId="7"/>
-    <sheet name="17.03 P1" r:id="rId2" sheetId="9"/>
-    <sheet name="Planilha1" r:id="rId3" sheetId="8" state="hidden"/>
+    <sheet name="envioPendenciaGOInspecao" sheetId="7" r:id="rId1"/>
+    <sheet name="17.03 P1" sheetId="9" r:id="rId2"/>
+    <sheet name="Planilha1" sheetId="8" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">envioPendenciaGOInspecao!$A$1:$M$135</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">envioPendenciaGOInspecao!$A$1:$M$135</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10506" uniqueCount="624">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1920" uniqueCount="623">
   <si>
     <t>NR PROPOSTA</t>
   </si>
@@ -1930,16 +1930,12 @@
     <t>762   (Nota)
 Parcerias Recusas BE53298     Privado
   21/11/2025</t>
-  </si>
-  <si>
-    <t>Alerta:</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -2001,34 +1997,34 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="8">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
-    <xf applyAlignment="1" applyFill="1" applyFont="1" borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" applyFill="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="14" xfId="0">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="1">
     <dxf>
@@ -2039,7 +2035,7 @@
       </fill>
     </dxf>
   </dxfs>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -2052,7 +2048,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
@@ -2153,7 +2149,7 @@
         </a:fontRef>
       </xdr:style>
       <xdr:txBody>
-        <a:bodyPr anchor="t" horzOverflow="clip" rtlCol="0" vertOverflow="clip"/>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
@@ -2194,7 +2190,7 @@
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst>
-            <a:gd fmla="val 50000" name="adj1"/>
+            <a:gd name="adj1" fmla="val 50000"/>
           </a:avLst>
         </a:prstGeom>
         <a:ln>
@@ -2268,7 +2264,7 @@
         </a:fontRef>
       </xdr:style>
       <xdr:txBody>
-        <a:bodyPr anchor="t" horzOverflow="clip" rtlCol="0" vertOverflow="clip"/>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
@@ -2277,7 +2273,7 @@
             <a:t>Usaremos este campo para informar qual nota será utilizada.</a:t>
           </a:r>
           <a:r>
-            <a:rPr baseline="0" lang="pt-BR" sz="1100"/>
+            <a:rPr lang="pt-BR" sz="1100" baseline="0"/>
             <a:t> Todo o fluxo continua sem alteração &gt; Pega a Proposta na coluna "A" e vai até a FG na plataforma, na lateral em Nota/Agenda utilizará a nota informada na coluna "I".</a:t>
           </a:r>
           <a:endParaRPr lang="pt-BR" sz="1100"/>
@@ -2294,10 +2290,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -2495,21 +2491,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="6350">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -2526,7 +2522,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -2578,33 +2574,33 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" name="Office Theme" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Planilha1">
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:M599"/>
+  <dimension ref="A1:L599"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="2" width="23.28515625" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" style="2" width="13.7109375" collapsed="true"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="2" width="6.7109375" collapsed="true"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="2" width="15.5703125" collapsed="true"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="2" width="22.0" collapsed="true"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="2" width="14.85546875" collapsed="true"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="2" width="10.28515625" collapsed="true"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="2" width="12.42578125" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" style="2" width="12.42578125" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="2" width="15.85546875" collapsed="true"/>
-    <col min="11" max="11" style="2" width="9.140625" collapsed="true"/>
-    <col min="12" max="12" customWidth="true" style="7" width="85.7109375" collapsed="true"/>
-    <col min="13" max="16384" style="2" width="9.140625" collapsed="true"/>
+    <col min="1" max="1" width="23.28515625" style="2" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="13.7109375" style="2" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="6.7109375" style="2" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="15.5703125" style="2" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="22" style="2" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="14.85546875" style="2" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="10.28515625" style="2" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="12.42578125" style="2" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="12.42578125" style="2" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="15.85546875" style="2" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="9.140625" style="2" collapsed="1"/>
+    <col min="12" max="12" width="85.7109375" style="7" customWidth="1" collapsed="1"/>
+    <col min="13" max="16384" width="9.140625" style="2" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -2645,7 +2641,7 @@
         <v>147</v>
       </c>
     </row>
-    <row customFormat="1" r="2" s="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>134990497</v>
       </c>
@@ -2683,7 +2679,7 @@
         <v>613</v>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>135243818</v>
       </c>
@@ -7047,9 +7043,7 @@
       <c r="K117" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="L117" t="s">
-        <v>623</v>
-      </c>
+      <c r="L117"/>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A118" s="2">
@@ -7085,9 +7079,7 @@
       <c r="K118" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="L118" t="s">
-        <v>623</v>
-      </c>
+      <c r="L118"/>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A119" s="2">
@@ -7123,9 +7115,7 @@
       <c r="K119" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="L119" t="s">
-        <v>623</v>
-      </c>
+      <c r="L119"/>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A120" s="2">
@@ -7161,9 +7151,7 @@
       <c r="K120" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="L120" t="s">
-        <v>623</v>
-      </c>
+      <c r="L120"/>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A121" s="2">
@@ -7199,9 +7187,7 @@
       <c r="K121" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="L121" t="s">
-        <v>623</v>
-      </c>
+      <c r="L121"/>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A122" s="2">
@@ -7237,9 +7223,7 @@
       <c r="K122" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="L122" t="s">
-        <v>623</v>
-      </c>
+      <c r="L122"/>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A123" s="2">
@@ -7275,9 +7259,7 @@
       <c r="K123" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="L123" t="s">
-        <v>623</v>
-      </c>
+      <c r="L123"/>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A124" s="2">
@@ -7313,9 +7295,7 @@
       <c r="K124" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="L124" t="s">
-        <v>623</v>
-      </c>
+      <c r="L124"/>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A125" s="2">
@@ -7351,9 +7331,7 @@
       <c r="K125" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="L125" t="s">
-        <v>623</v>
-      </c>
+      <c r="L125"/>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A126" s="2">
@@ -7389,9 +7367,7 @@
       <c r="K126" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="L126" t="s">
-        <v>623</v>
-      </c>
+      <c r="L126"/>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A127" s="2">
@@ -7427,9 +7403,7 @@
       <c r="K127" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="L127" t="s">
-        <v>623</v>
-      </c>
+      <c r="L127"/>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A128" s="2">
@@ -7465,9 +7439,7 @@
       <c r="K128" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="L128" t="s">
-        <v>623</v>
-      </c>
+      <c r="L128"/>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A129" s="2">
@@ -7503,9 +7475,7 @@
       <c r="K129" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="L129" t="s">
-        <v>623</v>
-      </c>
+      <c r="L129"/>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A130" s="2">
@@ -7541,9 +7511,7 @@
       <c r="K130" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="L130" t="s">
-        <v>623</v>
-      </c>
+      <c r="L130"/>
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A131" s="2">
@@ -7579,9 +7547,7 @@
       <c r="K131" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="L131" t="s">
-        <v>623</v>
-      </c>
+      <c r="L131"/>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A132" s="2">
@@ -7617,9 +7583,7 @@
       <c r="K132" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="L132" t="s">
-        <v>623</v>
-      </c>
+      <c r="L132"/>
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A133" s="2">
@@ -7655,9 +7619,7 @@
       <c r="K133" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="L133" t="s">
-        <v>623</v>
-      </c>
+      <c r="L133"/>
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A134" s="2">
@@ -7693,9 +7655,7 @@
       <c r="K134" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="L134" t="s">
-        <v>623</v>
-      </c>
+      <c r="L134"/>
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A135" s="2">
@@ -7731,9 +7691,7 @@
       <c r="K135" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="L135" t="s">
-        <v>623</v>
-      </c>
+      <c r="L135"/>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A136" s="2">
@@ -7769,9 +7727,7 @@
       <c r="K136" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="L136" t="s">
-        <v>623</v>
-      </c>
+      <c r="L136"/>
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A137" s="2">
@@ -7807,9 +7763,7 @@
       <c r="K137" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="L137" t="s">
-        <v>623</v>
-      </c>
+      <c r="L137"/>
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A138" s="2">
@@ -7845,9 +7799,7 @@
       <c r="K138" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="L138" t="s">
-        <v>623</v>
-      </c>
+      <c r="L138"/>
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A139" s="2">
@@ -7883,9 +7835,7 @@
       <c r="K139" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="L139" t="s">
-        <v>623</v>
-      </c>
+      <c r="L139"/>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A140" s="2">
@@ -7921,9 +7871,7 @@
       <c r="K140" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="L140" t="s">
-        <v>623</v>
-      </c>
+      <c r="L140"/>
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A141" s="2">
@@ -7959,9 +7907,7 @@
       <c r="K141" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="L141" t="s">
-        <v>623</v>
-      </c>
+      <c r="L141"/>
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A142" s="2">
@@ -7997,9 +7943,7 @@
       <c r="K142" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="L142" t="s">
-        <v>623</v>
-      </c>
+      <c r="L142"/>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A143" s="2">
@@ -8035,9 +7979,7 @@
       <c r="K143" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="L143" t="s">
-        <v>623</v>
-      </c>
+      <c r="L143"/>
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A144" s="2">
@@ -8073,9 +8015,7 @@
       <c r="K144" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="L144" t="s">
-        <v>623</v>
-      </c>
+      <c r="L144"/>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A145" s="2">
@@ -8111,9 +8051,7 @@
       <c r="K145" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="L145" t="s">
-        <v>623</v>
-      </c>
+      <c r="L145"/>
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A146" s="2">
@@ -8149,9 +8087,7 @@
       <c r="K146" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="L146" t="s">
-        <v>623</v>
-      </c>
+      <c r="L146"/>
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A147" s="2">
@@ -8187,9 +8123,7 @@
       <c r="K147" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="L147" t="s">
-        <v>623</v>
-      </c>
+      <c r="L147"/>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A148" s="2">
@@ -8225,9 +8159,7 @@
       <c r="K148" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="L148" t="s">
-        <v>623</v>
-      </c>
+      <c r="L148"/>
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A149" s="2">
@@ -8263,9 +8195,7 @@
       <c r="K149" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="L149" t="s">
-        <v>623</v>
-      </c>
+      <c r="L149"/>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A150" s="2">
@@ -8301,9 +8231,7 @@
       <c r="K150" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="L150" t="s">
-        <v>623</v>
-      </c>
+      <c r="L150"/>
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A151" s="2">
@@ -8339,9 +8267,7 @@
       <c r="K151" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="L151" t="s">
-        <v>623</v>
-      </c>
+      <c r="L151"/>
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A152" s="2">
@@ -8377,9 +8303,7 @@
       <c r="K152" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="L152" t="s">
-        <v>623</v>
-      </c>
+      <c r="L152"/>
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A153" s="2">
@@ -8415,9 +8339,7 @@
       <c r="K153" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="L153" t="s">
-        <v>623</v>
-      </c>
+      <c r="L153"/>
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A154" s="2">
@@ -8453,9 +8375,7 @@
       <c r="K154" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="L154" t="s">
-        <v>623</v>
-      </c>
+      <c r="L154"/>
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A155" s="2">
@@ -8491,9 +8411,7 @@
       <c r="K155" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="L155" t="s">
-        <v>623</v>
-      </c>
+      <c r="L155"/>
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A156" s="2">
@@ -8529,9 +8447,7 @@
       <c r="K156" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="L156" t="s">
-        <v>623</v>
-      </c>
+      <c r="L156"/>
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A157" s="2">
@@ -8567,9 +8483,7 @@
       <c r="K157" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="L157" t="s">
-        <v>623</v>
-      </c>
+      <c r="L157"/>
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A158" s="2">
@@ -8605,9 +8519,7 @@
       <c r="K158" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="L158" t="s">
-        <v>623</v>
-      </c>
+      <c r="L158"/>
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A159" s="2">
@@ -8643,9 +8555,7 @@
       <c r="K159" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="L159" t="s">
-        <v>623</v>
-      </c>
+      <c r="L159"/>
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A160" s="2">
@@ -8681,9 +8591,7 @@
       <c r="K160" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="L160" t="s">
-        <v>623</v>
-      </c>
+      <c r="L160"/>
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A161" s="2">
@@ -8719,9 +8627,7 @@
       <c r="K161" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="L161" t="s">
-        <v>623</v>
-      </c>
+      <c r="L161"/>
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A162" s="2">
@@ -8757,9 +8663,7 @@
       <c r="K162" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="L162" t="s">
-        <v>623</v>
-      </c>
+      <c r="L162"/>
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A163" s="2">
@@ -8795,9 +8699,7 @@
       <c r="K163" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="L163" t="s">
-        <v>623</v>
-      </c>
+      <c r="L163"/>
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A164" s="2">
@@ -8833,9 +8735,7 @@
       <c r="K164" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="L164" t="s">
-        <v>623</v>
-      </c>
+      <c r="L164"/>
     </row>
     <row r="165" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A165" s="2">
@@ -8871,9 +8771,7 @@
       <c r="K165" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="L165" t="s">
-        <v>623</v>
-      </c>
+      <c r="L165"/>
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A166" s="2">
@@ -8909,9 +8807,7 @@
       <c r="K166" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="L166" t="s">
-        <v>623</v>
-      </c>
+      <c r="L166"/>
     </row>
     <row r="167" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A167" s="2">
@@ -8947,9 +8843,7 @@
       <c r="K167" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="L167" t="s">
-        <v>623</v>
-      </c>
+      <c r="L167"/>
     </row>
     <row r="168" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A168" s="2">
@@ -8985,9 +8879,7 @@
       <c r="K168" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="L168" t="s">
-        <v>623</v>
-      </c>
+      <c r="L168"/>
     </row>
     <row r="169" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A169" s="2">
@@ -9023,9 +8915,7 @@
       <c r="K169" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="L169" t="s">
-        <v>623</v>
-      </c>
+      <c r="L169"/>
     </row>
     <row r="170" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A170" s="2">
@@ -9061,9 +8951,7 @@
       <c r="K170" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="L170" t="s">
-        <v>623</v>
-      </c>
+      <c r="L170"/>
     </row>
     <row r="171" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A171" s="2">
@@ -9099,9 +8987,7 @@
       <c r="K171" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="L171" t="s">
-        <v>623</v>
-      </c>
+      <c r="L171"/>
     </row>
     <row r="172" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A172" s="2">
@@ -9137,9 +9023,7 @@
       <c r="K172" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="L172" t="s">
-        <v>623</v>
-      </c>
+      <c r="L172"/>
     </row>
     <row r="173" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A173" s="2">
@@ -9175,9 +9059,7 @@
       <c r="K173" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="L173" t="s">
-        <v>623</v>
-      </c>
+      <c r="L173"/>
     </row>
     <row r="174" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A174" s="2">
@@ -9213,9 +9095,7 @@
       <c r="K174" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="L174" t="s">
-        <v>623</v>
-      </c>
+      <c r="L174"/>
     </row>
     <row r="175" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A175" s="2">
@@ -9251,9 +9131,7 @@
       <c r="K175" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="L175" t="s">
-        <v>623</v>
-      </c>
+      <c r="L175"/>
     </row>
     <row r="176" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A176" s="2">
@@ -9289,9 +9167,7 @@
       <c r="K176" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="L176" t="s">
-        <v>623</v>
-      </c>
+      <c r="L176"/>
     </row>
     <row r="177" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A177" s="2">
@@ -9327,9 +9203,7 @@
       <c r="K177" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="L177" t="s">
-        <v>623</v>
-      </c>
+      <c r="L177"/>
     </row>
     <row r="178" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A178" s="2">
@@ -9365,9 +9239,7 @@
       <c r="K178" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="L178" t="s">
-        <v>623</v>
-      </c>
+      <c r="L178"/>
     </row>
     <row r="179" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A179" s="2">
@@ -9403,9 +9275,7 @@
       <c r="K179" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="L179" t="s">
-        <v>623</v>
-      </c>
+      <c r="L179"/>
     </row>
     <row r="180" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A180" s="2">
@@ -9441,9 +9311,7 @@
       <c r="K180" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="L180" t="s">
-        <v>623</v>
-      </c>
+      <c r="L180"/>
     </row>
     <row r="181" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A181" s="2">
@@ -9479,9 +9347,7 @@
       <c r="K181" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="L181" t="s">
-        <v>623</v>
-      </c>
+      <c r="L181"/>
     </row>
     <row r="182" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A182" s="2">
@@ -9517,9 +9383,7 @@
       <c r="K182" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="L182" t="s">
-        <v>623</v>
-      </c>
+      <c r="L182"/>
     </row>
     <row r="183" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A183" s="2">
@@ -9555,9 +9419,7 @@
       <c r="K183" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="L183" t="s">
-        <v>623</v>
-      </c>
+      <c r="L183"/>
     </row>
     <row r="184" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A184" s="2">
@@ -9593,9 +9455,7 @@
       <c r="K184" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="L184" t="s">
-        <v>623</v>
-      </c>
+      <c r="L184"/>
     </row>
     <row r="185" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A185" s="2">
@@ -9631,9 +9491,7 @@
       <c r="K185" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="L185" t="s">
-        <v>623</v>
-      </c>
+      <c r="L185"/>
     </row>
     <row r="186" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A186" s="2">
@@ -9669,9 +9527,7 @@
       <c r="K186" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="L186" t="s">
-        <v>623</v>
-      </c>
+      <c r="L186"/>
     </row>
     <row r="187" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A187" s="2">
@@ -9707,9 +9563,7 @@
       <c r="K187" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="L187" t="s">
-        <v>623</v>
-      </c>
+      <c r="L187"/>
     </row>
     <row r="188" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A188" s="2">
@@ -9745,9 +9599,7 @@
       <c r="K188" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="L188" t="s">
-        <v>623</v>
-      </c>
+      <c r="L188"/>
     </row>
     <row r="189" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A189" s="2">
@@ -9783,9 +9635,7 @@
       <c r="K189" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="L189" t="s">
-        <v>623</v>
-      </c>
+      <c r="L189"/>
     </row>
     <row r="190" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A190" s="2">
@@ -9821,9 +9671,7 @@
       <c r="K190" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="L190" t="s">
-        <v>623</v>
-      </c>
+      <c r="L190"/>
     </row>
     <row r="191" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A191" s="2">
@@ -9859,9 +9707,7 @@
       <c r="K191" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="L191" t="s">
-        <v>623</v>
-      </c>
+      <c r="L191"/>
     </row>
     <row r="192" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A192" s="2">
@@ -9897,9 +9743,7 @@
       <c r="K192" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="L192" t="s">
-        <v>623</v>
-      </c>
+      <c r="L192"/>
     </row>
     <row r="193" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A193" s="2">
@@ -9935,9 +9779,7 @@
       <c r="K193" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="L193" t="s">
-        <v>623</v>
-      </c>
+      <c r="L193"/>
     </row>
     <row r="194" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A194" s="2">
@@ -9973,9 +9815,7 @@
       <c r="K194" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="L194" t="s">
-        <v>623</v>
-      </c>
+      <c r="L194"/>
     </row>
     <row r="195" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A195" s="2">
@@ -10011,9 +9851,7 @@
       <c r="K195" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="L195" t="s">
-        <v>623</v>
-      </c>
+      <c r="L195"/>
     </row>
     <row r="196" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A196" s="2">
@@ -10049,9 +9887,7 @@
       <c r="K196" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="L196" t="s">
-        <v>623</v>
-      </c>
+      <c r="L196"/>
     </row>
     <row r="197" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A197" s="2">
@@ -10087,9 +9923,7 @@
       <c r="K197" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="L197" t="s">
-        <v>623</v>
-      </c>
+      <c r="L197"/>
     </row>
     <row r="198" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A198" s="2">
@@ -10125,9 +9959,7 @@
       <c r="K198" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="L198" t="s">
-        <v>623</v>
-      </c>
+      <c r="L198"/>
     </row>
     <row r="199" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A199" s="2">
@@ -10163,9 +9995,7 @@
       <c r="K199" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="L199" t="s">
-        <v>623</v>
-      </c>
+      <c r="L199"/>
     </row>
     <row r="200" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A200" s="2">
@@ -10201,9 +10031,7 @@
       <c r="K200" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="L200" t="s">
-        <v>623</v>
-      </c>
+      <c r="L200"/>
     </row>
     <row r="201" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A201" s="2">
@@ -10239,9 +10067,7 @@
       <c r="K201" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="L201" t="s">
-        <v>623</v>
-      </c>
+      <c r="L201"/>
     </row>
     <row r="202" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A202" s="2">
@@ -10277,9 +10103,7 @@
       <c r="K202" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="L202" t="s">
-        <v>623</v>
-      </c>
+      <c r="L202"/>
     </row>
     <row r="203" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A203" s="2">
@@ -10315,9 +10139,7 @@
       <c r="K203" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="L203" t="s">
-        <v>623</v>
-      </c>
+      <c r="L203"/>
     </row>
     <row r="204" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A204" s="2">
@@ -10353,9 +10175,7 @@
       <c r="K204" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="L204" t="s">
-        <v>623</v>
-      </c>
+      <c r="L204"/>
     </row>
     <row r="205" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A205" s="2">
@@ -10391,9 +10211,7 @@
       <c r="K205" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="L205" t="s">
-        <v>623</v>
-      </c>
+      <c r="L205"/>
     </row>
     <row r="206" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A206" s="2">
@@ -10429,9 +10247,7 @@
       <c r="K206" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="L206" t="s">
-        <v>623</v>
-      </c>
+      <c r="L206"/>
     </row>
     <row r="207" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A207" s="2">
@@ -10467,9 +10283,7 @@
       <c r="K207" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="L207" t="s">
-        <v>623</v>
-      </c>
+      <c r="L207"/>
     </row>
     <row r="208" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A208" s="2">
@@ -10505,9 +10319,7 @@
       <c r="K208" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="L208" t="s">
-        <v>623</v>
-      </c>
+      <c r="L208"/>
     </row>
     <row r="209" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A209" s="2">
@@ -10543,9 +10355,7 @@
       <c r="K209" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="L209" t="s">
-        <v>623</v>
-      </c>
+      <c r="L209"/>
     </row>
     <row r="210" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A210" s="2">
@@ -10581,9 +10391,7 @@
       <c r="K210" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="L210" t="s">
-        <v>623</v>
-      </c>
+      <c r="L210"/>
     </row>
     <row r="211" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A211" s="2">
@@ -10619,9 +10427,7 @@
       <c r="K211" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="L211" t="s">
-        <v>623</v>
-      </c>
+      <c r="L211"/>
     </row>
     <row r="212" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A212" s="2">
@@ -10657,9 +10463,7 @@
       <c r="K212" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="L212" t="s">
-        <v>623</v>
-      </c>
+      <c r="L212"/>
     </row>
     <row r="213" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A213" s="2">
@@ -10695,9 +10499,7 @@
       <c r="K213" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="L213" t="s">
-        <v>623</v>
-      </c>
+      <c r="L213"/>
     </row>
     <row r="214" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A214" s="2">
@@ -10733,9 +10535,7 @@
       <c r="K214" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="L214" t="s">
-        <v>623</v>
-      </c>
+      <c r="L214"/>
     </row>
     <row r="215" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A215" s="2">
@@ -10771,9 +10571,7 @@
       <c r="K215" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="L215" t="s">
-        <v>623</v>
-      </c>
+      <c r="L215"/>
     </row>
     <row r="216" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A216" s="2">
@@ -10809,9 +10607,7 @@
       <c r="K216" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="L216" t="s">
-        <v>623</v>
-      </c>
+      <c r="L216"/>
     </row>
     <row r="217" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A217" s="2">
@@ -10847,9 +10643,7 @@
       <c r="K217" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="L217" t="s">
-        <v>623</v>
-      </c>
+      <c r="L217"/>
     </row>
     <row r="218" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A218" s="2">
@@ -10885,9 +10679,7 @@
       <c r="K218" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="L218" t="s">
-        <v>623</v>
-      </c>
+      <c r="L218"/>
     </row>
     <row r="219" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A219" s="2">
@@ -10923,9 +10715,7 @@
       <c r="K219" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="L219" t="s">
-        <v>623</v>
-      </c>
+      <c r="L219"/>
     </row>
     <row r="220" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A220" s="2">
@@ -10961,9 +10751,7 @@
       <c r="K220" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="L220" t="s">
-        <v>623</v>
-      </c>
+      <c r="L220"/>
     </row>
     <row r="221" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A221" s="2">
@@ -10999,9 +10787,7 @@
       <c r="K221" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="L221" t="s">
-        <v>623</v>
-      </c>
+      <c r="L221"/>
     </row>
     <row r="222" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A222" s="2">
@@ -11037,9 +10823,7 @@
       <c r="K222" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="L222" t="s">
-        <v>623</v>
-      </c>
+      <c r="L222"/>
     </row>
     <row r="223" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A223" s="2">
@@ -11075,9 +10859,7 @@
       <c r="K223" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="L223" t="s">
-        <v>623</v>
-      </c>
+      <c r="L223"/>
     </row>
     <row r="224" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A224" s="2">
@@ -11113,9 +10895,7 @@
       <c r="K224" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="L224" t="s">
-        <v>623</v>
-      </c>
+      <c r="L224"/>
     </row>
     <row r="225" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A225" s="2">
@@ -11151,9 +10931,7 @@
       <c r="K225" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="L225" t="s">
-        <v>623</v>
-      </c>
+      <c r="L225"/>
     </row>
     <row r="226" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A226" s="2">
@@ -11189,9 +10967,7 @@
       <c r="K226" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="L226" t="s">
-        <v>623</v>
-      </c>
+      <c r="L226"/>
     </row>
     <row r="227" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A227" s="2">
@@ -11227,9 +11003,7 @@
       <c r="K227" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="L227" t="s">
-        <v>623</v>
-      </c>
+      <c r="L227"/>
     </row>
     <row r="228" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A228" s="2">
@@ -11265,9 +11039,7 @@
       <c r="K228" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="L228" t="s">
-        <v>623</v>
-      </c>
+      <c r="L228"/>
     </row>
     <row r="229" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A229" s="2">
@@ -11303,9 +11075,7 @@
       <c r="K229" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="L229" t="s">
-        <v>623</v>
-      </c>
+      <c r="L229"/>
     </row>
     <row r="230" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A230" s="2">
@@ -11341,9 +11111,7 @@
       <c r="K230" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="L230" t="s">
-        <v>623</v>
-      </c>
+      <c r="L230"/>
     </row>
     <row r="231" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A231" s="2">
@@ -11379,9 +11147,7 @@
       <c r="K231" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="L231" t="s">
-        <v>623</v>
-      </c>
+      <c r="L231"/>
     </row>
     <row r="232" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A232" s="2">
@@ -11417,9 +11183,7 @@
       <c r="K232" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="L232" t="s">
-        <v>623</v>
-      </c>
+      <c r="L232"/>
     </row>
     <row r="233" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A233" s="2">
@@ -11455,9 +11219,7 @@
       <c r="K233" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="L233" t="s">
-        <v>623</v>
-      </c>
+      <c r="L233"/>
     </row>
     <row r="234" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A234" s="2">
@@ -11493,9 +11255,7 @@
       <c r="K234" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="L234" t="s">
-        <v>623</v>
-      </c>
+      <c r="L234"/>
     </row>
     <row r="235" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A235" s="2">
@@ -11531,9 +11291,7 @@
       <c r="K235" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="L235" t="s">
-        <v>623</v>
-      </c>
+      <c r="L235"/>
     </row>
     <row r="236" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A236" s="2">
@@ -11569,9 +11327,7 @@
       <c r="K236" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="L236" t="s">
-        <v>623</v>
-      </c>
+      <c r="L236"/>
     </row>
     <row r="237" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A237" s="2">
@@ -11607,9 +11363,7 @@
       <c r="K237" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="L237" t="s">
-        <v>623</v>
-      </c>
+      <c r="L237"/>
     </row>
     <row r="238" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A238" s="2">
@@ -11645,9 +11399,7 @@
       <c r="K238" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="L238" t="s">
-        <v>623</v>
-      </c>
+      <c r="L238"/>
     </row>
     <row r="239" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A239" s="2">
@@ -11683,9 +11435,7 @@
       <c r="K239" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="L239" t="s">
-        <v>623</v>
-      </c>
+      <c r="L239"/>
     </row>
     <row r="240" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A240" s="2">
@@ -11721,9 +11471,7 @@
       <c r="K240" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="L240" t="s">
-        <v>623</v>
-      </c>
+      <c r="L240"/>
     </row>
     <row r="241" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A241" s="2">
@@ -11759,9 +11507,7 @@
       <c r="K241" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="L241" t="s">
-        <v>623</v>
-      </c>
+      <c r="L241"/>
     </row>
     <row r="242" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A242" s="2">
@@ -11797,9 +11543,7 @@
       <c r="K242" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="L242" t="s">
-        <v>623</v>
-      </c>
+      <c r="L242"/>
     </row>
     <row r="243" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A243" s="2">
@@ -11835,9 +11579,7 @@
       <c r="K243" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="L243" t="s">
-        <v>623</v>
-      </c>
+      <c r="L243"/>
     </row>
     <row r="244" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A244" s="2">
@@ -11873,9 +11615,7 @@
       <c r="K244" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="L244" t="s">
-        <v>623</v>
-      </c>
+      <c r="L244"/>
     </row>
     <row r="245" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A245" s="2">
@@ -11911,9 +11651,7 @@
       <c r="K245" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="L245" t="s">
-        <v>623</v>
-      </c>
+      <c r="L245"/>
     </row>
     <row r="246" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A246" s="2">
@@ -11949,9 +11687,7 @@
       <c r="K246" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="L246" t="s">
-        <v>623</v>
-      </c>
+      <c r="L246"/>
     </row>
     <row r="247" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A247" s="2">
@@ -11987,9 +11723,7 @@
       <c r="K247" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="L247" t="s">
-        <v>623</v>
-      </c>
+      <c r="L247"/>
     </row>
     <row r="248" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A248" s="2">
@@ -12025,9 +11759,7 @@
       <c r="K248" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="L248" t="s">
-        <v>623</v>
-      </c>
+      <c r="L248"/>
     </row>
     <row r="249" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A249" s="2">
@@ -12063,9 +11795,7 @@
       <c r="K249" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="L249" t="s">
-        <v>623</v>
-      </c>
+      <c r="L249"/>
     </row>
     <row r="250" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A250" s="2">
@@ -12101,9 +11831,7 @@
       <c r="K250" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="L250" t="s">
-        <v>623</v>
-      </c>
+      <c r="L250"/>
     </row>
     <row r="251" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A251" s="2">
@@ -12139,9 +11867,7 @@
       <c r="K251" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="L251" t="s">
-        <v>623</v>
-      </c>
+      <c r="L251"/>
     </row>
     <row r="252" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A252" s="2">
@@ -12177,9 +11903,7 @@
       <c r="K252" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="L252" t="s">
-        <v>623</v>
-      </c>
+      <c r="L252"/>
     </row>
     <row r="253" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A253" s="2">
@@ -12215,9 +11939,7 @@
       <c r="K253" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="L253" t="s">
-        <v>623</v>
-      </c>
+      <c r="L253"/>
     </row>
     <row r="254" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A254" s="2">
@@ -12253,9 +11975,7 @@
       <c r="K254" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="L254" t="s">
-        <v>623</v>
-      </c>
+      <c r="L254"/>
     </row>
     <row r="255" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A255" s="2">
@@ -12291,9 +12011,7 @@
       <c r="K255" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="L255" t="s">
-        <v>623</v>
-      </c>
+      <c r="L255"/>
     </row>
     <row r="256" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A256" s="2">
@@ -12329,9 +12047,7 @@
       <c r="K256" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="L256" t="s">
-        <v>623</v>
-      </c>
+      <c r="L256"/>
     </row>
     <row r="257" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A257" s="2">
@@ -12367,9 +12083,7 @@
       <c r="K257" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="L257" t="s">
-        <v>623</v>
-      </c>
+      <c r="L257"/>
     </row>
     <row r="258" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A258" s="2">
@@ -12405,9 +12119,7 @@
       <c r="K258" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="L258" t="s">
-        <v>623</v>
-      </c>
+      <c r="L258"/>
     </row>
     <row r="259" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A259" s="2">
@@ -12443,9 +12155,7 @@
       <c r="K259" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="L259" t="s">
-        <v>623</v>
-      </c>
+      <c r="L259"/>
     </row>
     <row r="260" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A260" s="2">
@@ -12481,9 +12191,7 @@
       <c r="K260" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="L260" t="s">
-        <v>623</v>
-      </c>
+      <c r="L260"/>
     </row>
     <row r="261" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A261" s="2">
@@ -12519,9 +12227,7 @@
       <c r="K261" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="L261" t="s">
-        <v>623</v>
-      </c>
+      <c r="L261"/>
     </row>
     <row r="262" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A262" s="2">
@@ -12557,9 +12263,7 @@
       <c r="K262" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="L262" t="s">
-        <v>623</v>
-      </c>
+      <c r="L262"/>
     </row>
     <row r="263" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A263" s="2">
@@ -12595,9 +12299,7 @@
       <c r="K263" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="L263" t="s">
-        <v>623</v>
-      </c>
+      <c r="L263"/>
     </row>
     <row r="264" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A264" s="2">
@@ -12633,9 +12335,7 @@
       <c r="K264" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="L264" t="s">
-        <v>623</v>
-      </c>
+      <c r="L264"/>
     </row>
     <row r="265" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A265" s="2">
@@ -12671,9 +12371,7 @@
       <c r="K265" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="L265" t="s">
-        <v>623</v>
-      </c>
+      <c r="L265"/>
     </row>
     <row r="266" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A266" s="2">
@@ -12709,9 +12407,7 @@
       <c r="K266" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="L266" t="s">
-        <v>623</v>
-      </c>
+      <c r="L266"/>
     </row>
     <row r="267" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A267" s="2">
@@ -12747,9 +12443,7 @@
       <c r="K267" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="L267" t="s">
-        <v>623</v>
-      </c>
+      <c r="L267"/>
     </row>
     <row r="268" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A268" s="2">
@@ -12785,9 +12479,7 @@
       <c r="K268" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="L268" t="s">
-        <v>623</v>
-      </c>
+      <c r="L268"/>
     </row>
     <row r="269" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A269" s="2">
@@ -12823,9 +12515,7 @@
       <c r="K269" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="L269" t="s">
-        <v>623</v>
-      </c>
+      <c r="L269"/>
     </row>
     <row r="270" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A270" s="2">
@@ -12861,9 +12551,7 @@
       <c r="K270" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="L270" t="s">
-        <v>623</v>
-      </c>
+      <c r="L270"/>
     </row>
     <row r="271" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A271" s="2">
@@ -12899,9 +12587,7 @@
       <c r="K271" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="L271" t="s">
-        <v>623</v>
-      </c>
+      <c r="L271"/>
     </row>
     <row r="272" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A272" s="2">
@@ -12937,9 +12623,7 @@
       <c r="K272" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="L272" t="s">
-        <v>623</v>
-      </c>
+      <c r="L272"/>
     </row>
     <row r="273" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A273" s="2">
@@ -12975,9 +12659,7 @@
       <c r="K273" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="L273" t="s">
-        <v>623</v>
-      </c>
+      <c r="L273"/>
     </row>
     <row r="274" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A274" s="2">
@@ -13013,9 +12695,7 @@
       <c r="K274" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="L274" t="s">
-        <v>623</v>
-      </c>
+      <c r="L274"/>
     </row>
     <row r="275" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A275" s="2">
@@ -13051,9 +12731,7 @@
       <c r="K275" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="L275" t="s">
-        <v>623</v>
-      </c>
+      <c r="L275"/>
     </row>
     <row r="276" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A276" s="2">
@@ -13089,9 +12767,7 @@
       <c r="K276" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="L276" t="s">
-        <v>623</v>
-      </c>
+      <c r="L276"/>
     </row>
     <row r="277" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A277" s="2">
@@ -13127,9 +12803,7 @@
       <c r="K277" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="L277" t="s">
-        <v>623</v>
-      </c>
+      <c r="L277"/>
     </row>
     <row r="278" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A278" s="2">
@@ -13165,9 +12839,7 @@
       <c r="K278" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="L278" t="s">
-        <v>623</v>
-      </c>
+      <c r="L278"/>
     </row>
     <row r="279" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A279" s="2">
@@ -13203,9 +12875,7 @@
       <c r="K279" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="L279" t="s">
-        <v>623</v>
-      </c>
+      <c r="L279"/>
     </row>
     <row r="280" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A280" s="2">
@@ -13241,9 +12911,7 @@
       <c r="K280" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="L280" t="s">
-        <v>623</v>
-      </c>
+      <c r="L280"/>
     </row>
     <row r="281" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A281" s="2">
@@ -13279,9 +12947,7 @@
       <c r="K281" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="L281" t="s">
-        <v>623</v>
-      </c>
+      <c r="L281"/>
     </row>
     <row r="282" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A282" s="2">
@@ -13317,9 +12983,7 @@
       <c r="K282" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="L282" t="s">
-        <v>623</v>
-      </c>
+      <c r="L282"/>
     </row>
     <row r="283" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A283" s="2">
@@ -13355,9 +13019,7 @@
       <c r="K283" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="L283" t="s">
-        <v>623</v>
-      </c>
+      <c r="L283"/>
     </row>
     <row r="284" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A284" s="2">
@@ -13393,9 +13055,7 @@
       <c r="K284" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="L284" t="s">
-        <v>623</v>
-      </c>
+      <c r="L284"/>
     </row>
     <row r="285" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A285" s="2">
@@ -13431,9 +13091,7 @@
       <c r="K285" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="L285" t="s">
-        <v>623</v>
-      </c>
+      <c r="L285"/>
     </row>
     <row r="286" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A286" s="2">
@@ -13469,9 +13127,7 @@
       <c r="K286" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="L286" t="s">
-        <v>623</v>
-      </c>
+      <c r="L286"/>
     </row>
     <row r="287" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A287" s="2">
@@ -13507,9 +13163,7 @@
       <c r="K287" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="L287" t="s">
-        <v>623</v>
-      </c>
+      <c r="L287"/>
     </row>
     <row r="288" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A288" s="2">
@@ -13545,9 +13199,7 @@
       <c r="K288" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="L288" t="s">
-        <v>623</v>
-      </c>
+      <c r="L288"/>
     </row>
     <row r="289" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A289" s="2">
@@ -13583,9 +13235,7 @@
       <c r="K289" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="L289" t="s">
-        <v>623</v>
-      </c>
+      <c r="L289"/>
     </row>
     <row r="290" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A290" s="2">
@@ -13621,9 +13271,7 @@
       <c r="K290" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="L290" t="s">
-        <v>623</v>
-      </c>
+      <c r="L290"/>
     </row>
     <row r="291" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A291" s="2">
@@ -13659,9 +13307,7 @@
       <c r="K291" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="L291" t="s">
-        <v>623</v>
-      </c>
+      <c r="L291"/>
     </row>
     <row r="292" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A292" s="2">
@@ -13697,9 +13343,7 @@
       <c r="K292" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="L292" t="s">
-        <v>623</v>
-      </c>
+      <c r="L292"/>
     </row>
     <row r="293" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A293" s="2">
@@ -13735,9 +13379,7 @@
       <c r="K293" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="L293" t="s">
-        <v>623</v>
-      </c>
+      <c r="L293"/>
     </row>
     <row r="294" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A294" s="2">
@@ -13773,9 +13415,7 @@
       <c r="K294" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="L294" t="s">
-        <v>623</v>
-      </c>
+      <c r="L294"/>
     </row>
     <row r="295" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A295" s="2">
@@ -13811,9 +13451,7 @@
       <c r="K295" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="L295" t="s">
-        <v>623</v>
-      </c>
+      <c r="L295"/>
     </row>
     <row r="296" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A296" s="2">
@@ -13849,9 +13487,7 @@
       <c r="K296" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="L296" t="s">
-        <v>623</v>
-      </c>
+      <c r="L296"/>
     </row>
     <row r="297" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A297" s="2">
@@ -13887,9 +13523,7 @@
       <c r="K297" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="L297" t="s">
-        <v>623</v>
-      </c>
+      <c r="L297"/>
     </row>
     <row r="298" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A298" s="2">
@@ -13925,9 +13559,7 @@
       <c r="K298" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="L298" t="s">
-        <v>623</v>
-      </c>
+      <c r="L298"/>
     </row>
     <row r="299" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A299" s="2">
@@ -13963,9 +13595,7 @@
       <c r="K299" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="L299" t="s">
-        <v>623</v>
-      </c>
+      <c r="L299"/>
     </row>
     <row r="300" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A300" s="2">
@@ -14001,9 +13631,7 @@
       <c r="K300" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="L300" t="s">
-        <v>623</v>
-      </c>
+      <c r="L300"/>
     </row>
     <row r="301" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A301" s="2">
@@ -14039,9 +13667,7 @@
       <c r="K301" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="L301" t="s">
-        <v>623</v>
-      </c>
+      <c r="L301"/>
     </row>
     <row r="302" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A302" s="2">
@@ -14077,9 +13703,7 @@
       <c r="K302" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="L302" t="s">
-        <v>623</v>
-      </c>
+      <c r="L302"/>
     </row>
     <row r="303" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A303" s="2">
@@ -14115,9 +13739,7 @@
       <c r="K303" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="L303" t="s">
-        <v>623</v>
-      </c>
+      <c r="L303"/>
     </row>
     <row r="304" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A304" s="2">
@@ -14153,11 +13775,9 @@
       <c r="K304" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="L304" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="305" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L304"/>
+    </row>
+    <row r="305" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A305" s="2">
         <v>888212749</v>
       </c>
@@ -14191,11 +13811,9 @@
       <c r="K305" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="L305" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="306" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L305"/>
+    </row>
+    <row r="306" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A306" s="2">
         <v>888212752</v>
       </c>
@@ -14229,11 +13847,9 @@
       <c r="K306" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="L306" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="307" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L306"/>
+    </row>
+    <row r="307" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A307" s="2">
         <v>888212753</v>
       </c>
@@ -14267,11 +13883,9 @@
       <c r="K307" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="L307" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="308" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L307"/>
+    </row>
+    <row r="308" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A308" s="2">
         <v>888212756</v>
       </c>
@@ -14305,11 +13919,9 @@
       <c r="K308" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="L308" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="309" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L308"/>
+    </row>
+    <row r="309" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A309" s="2">
         <v>888212764</v>
       </c>
@@ -14343,11 +13955,9 @@
       <c r="K309" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="L309" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="310" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L309"/>
+    </row>
+    <row r="310" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A310" s="2">
         <v>888212765</v>
       </c>
@@ -14381,11 +13991,9 @@
       <c r="K310" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="L310" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="311" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L310"/>
+    </row>
+    <row r="311" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A311" s="2">
         <v>888212766</v>
       </c>
@@ -14419,11 +14027,9 @@
       <c r="K311" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="L311" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="312" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L311"/>
+    </row>
+    <row r="312" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A312" s="2">
         <v>888212771</v>
       </c>
@@ -14457,11 +14063,9 @@
       <c r="K312" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="L312" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="313" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L312"/>
+    </row>
+    <row r="313" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A313" s="2">
         <v>888212773</v>
       </c>
@@ -14495,11 +14099,9 @@
       <c r="K313" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="L313" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="314" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L313"/>
+    </row>
+    <row r="314" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A314" s="2">
         <v>888212777</v>
       </c>
@@ -14533,11 +14135,9 @@
       <c r="K314" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="L314" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="315" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L314"/>
+    </row>
+    <row r="315" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A315" s="2">
         <v>888212778</v>
       </c>
@@ -14571,11 +14171,9 @@
       <c r="K315" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="L315" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="316" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L315"/>
+    </row>
+    <row r="316" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A316" s="2">
         <v>135416810</v>
       </c>
@@ -14609,11 +14207,9 @@
       <c r="K316" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="L316" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="317" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L316"/>
+    </row>
+    <row r="317" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A317" s="2">
         <v>135417074</v>
       </c>
@@ -14647,11 +14243,9 @@
       <c r="K317" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="L317" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="318" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L317"/>
+    </row>
+    <row r="318" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A318" s="2">
         <v>135417080</v>
       </c>
@@ -14685,11 +14279,9 @@
       <c r="K318" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="L318" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="319" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L318"/>
+    </row>
+    <row r="319" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A319" s="2">
         <v>135417116</v>
       </c>
@@ -14723,11 +14315,9 @@
       <c r="K319" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="L319" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="320" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L319"/>
+    </row>
+    <row r="320" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A320" s="2">
         <v>135417121</v>
       </c>
@@ -14761,11 +14351,9 @@
       <c r="K320" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="L320" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="321" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L320"/>
+    </row>
+    <row r="321" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A321" s="2">
         <v>135417132</v>
       </c>
@@ -14799,11 +14387,9 @@
       <c r="K321" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="L321" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="322" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L321"/>
+    </row>
+    <row r="322" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A322" s="2">
         <v>135417881</v>
       </c>
@@ -14837,11 +14423,9 @@
       <c r="K322" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="L322" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="323" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L322"/>
+    </row>
+    <row r="323" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A323" s="2">
         <v>135419206</v>
       </c>
@@ -14875,11 +14459,9 @@
       <c r="K323" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="L323" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="324" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L323"/>
+    </row>
+    <row r="324" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A324" s="2">
         <v>135419334</v>
       </c>
@@ -14913,11 +14495,9 @@
       <c r="K324" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="L324" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="325" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L324"/>
+    </row>
+    <row r="325" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A325" s="2">
         <v>135419460</v>
       </c>
@@ -14951,11 +14531,9 @@
       <c r="K325" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="L325" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="326" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L325"/>
+    </row>
+    <row r="326" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A326" s="2">
         <v>135419759</v>
       </c>
@@ -14989,11 +14567,9 @@
       <c r="K326" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="L326" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="327" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L326"/>
+    </row>
+    <row r="327" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A327" s="2">
         <v>135419956</v>
       </c>
@@ -15027,11 +14603,9 @@
       <c r="K327" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="L327" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="328" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L327"/>
+    </row>
+    <row r="328" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A328" s="2">
         <v>135420101</v>
       </c>
@@ -15065,11 +14639,9 @@
       <c r="K328" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="L328" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="329" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L328"/>
+    </row>
+    <row r="329" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A329" s="2">
         <v>135420239</v>
       </c>
@@ -15103,11 +14675,9 @@
       <c r="K329" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="L329" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="330" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L329"/>
+    </row>
+    <row r="330" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A330" s="2">
         <v>135420781</v>
       </c>
@@ -15141,11 +14711,9 @@
       <c r="K330" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="L330" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="331" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L330"/>
+    </row>
+    <row r="331" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A331" s="2">
         <v>135420801</v>
       </c>
@@ -15179,11 +14747,9 @@
       <c r="K331" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="L331" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="332" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L331"/>
+    </row>
+    <row r="332" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A332" s="2">
         <v>135420866</v>
       </c>
@@ -15217,11 +14783,9 @@
       <c r="K332" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="L332" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="333" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L332"/>
+    </row>
+    <row r="333" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A333" s="2">
         <v>135421060</v>
       </c>
@@ -15255,11 +14819,9 @@
       <c r="K333" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="L333" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="334" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L333"/>
+    </row>
+    <row r="334" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A334" s="2">
         <v>135421237</v>
       </c>
@@ -15293,11 +14855,9 @@
       <c r="K334" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="L334" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="335" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L334"/>
+    </row>
+    <row r="335" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A335" s="2">
         <v>135421955</v>
       </c>
@@ -15331,11 +14891,9 @@
       <c r="K335" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="L335" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="336" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L335"/>
+    </row>
+    <row r="336" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A336" s="2">
         <v>135422370</v>
       </c>
@@ -15369,11 +14927,9 @@
       <c r="K336" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="L336" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="337" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L336"/>
+    </row>
+    <row r="337" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A337" s="2">
         <v>135422607</v>
       </c>
@@ -15407,11 +14963,9 @@
       <c r="K337" s="3" t="s">
         <v>349</v>
       </c>
-      <c r="L337" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="338" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L337"/>
+    </row>
+    <row r="338" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A338" s="2">
         <v>135422971</v>
       </c>
@@ -15445,11 +14999,9 @@
       <c r="K338" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="L338" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="339" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L338"/>
+    </row>
+    <row r="339" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A339" s="2">
         <v>135423954</v>
       </c>
@@ -15483,11 +15035,9 @@
       <c r="K339" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="L339" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="340" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L339"/>
+    </row>
+    <row r="340" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A340" s="2">
         <v>135424615</v>
       </c>
@@ -15521,11 +15071,9 @@
       <c r="K340" s="3" t="s">
         <v>352</v>
       </c>
-      <c r="L340" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="341" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L340"/>
+    </row>
+    <row r="341" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A341" s="2">
         <v>135425607</v>
       </c>
@@ -15559,11 +15107,9 @@
       <c r="K341" s="3" t="s">
         <v>353</v>
       </c>
-      <c r="L341" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="342" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L341"/>
+    </row>
+    <row r="342" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A342" s="2">
         <v>135425986</v>
       </c>
@@ -15597,11 +15143,9 @@
       <c r="K342" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="L342" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="343" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L342"/>
+    </row>
+    <row r="343" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A343" s="2">
         <v>135426275</v>
       </c>
@@ -15635,11 +15179,9 @@
       <c r="K343" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="L343" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="344" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L343"/>
+    </row>
+    <row r="344" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A344" s="2">
         <v>135426741</v>
       </c>
@@ -15673,11 +15215,9 @@
       <c r="K344" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="L344" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="345" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L344"/>
+    </row>
+    <row r="345" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A345" s="2">
         <v>135426745</v>
       </c>
@@ -15711,11 +15251,9 @@
       <c r="K345" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="L345" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="346" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L345"/>
+    </row>
+    <row r="346" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A346" s="2">
         <v>135427490</v>
       </c>
@@ -15749,11 +15287,9 @@
       <c r="K346" s="3" t="s">
         <v>358</v>
       </c>
-      <c r="L346" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="347" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L346"/>
+    </row>
+    <row r="347" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A347" s="2">
         <v>135427589</v>
       </c>
@@ -15787,11 +15323,9 @@
       <c r="K347" s="3" t="s">
         <v>359</v>
       </c>
-      <c r="L347" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="348" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L347"/>
+    </row>
+    <row r="348" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A348" s="2">
         <v>135428052</v>
       </c>
@@ -15825,11 +15359,9 @@
       <c r="K348" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="L348" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="349" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L348"/>
+    </row>
+    <row r="349" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A349" s="2">
         <v>135428203</v>
       </c>
@@ -15863,11 +15395,9 @@
       <c r="K349" s="3" t="s">
         <v>361</v>
       </c>
-      <c r="L349" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="350" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L349"/>
+    </row>
+    <row r="350" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A350" s="2">
         <v>135428369</v>
       </c>
@@ -15901,11 +15431,9 @@
       <c r="K350" s="3" t="s">
         <v>362</v>
       </c>
-      <c r="L350" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="351" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L350"/>
+    </row>
+    <row r="351" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A351" s="2">
         <v>135428425</v>
       </c>
@@ -15939,11 +15467,9 @@
       <c r="K351" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="L351" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="352" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L351"/>
+    </row>
+    <row r="352" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A352" s="2">
         <v>135428702</v>
       </c>
@@ -15977,11 +15503,9 @@
       <c r="K352" s="3" t="s">
         <v>364</v>
       </c>
-      <c r="L352" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="353" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L352"/>
+    </row>
+    <row r="353" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A353" s="2">
         <v>135428753</v>
       </c>
@@ -16015,11 +15539,9 @@
       <c r="K353" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="L353" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="354" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L353"/>
+    </row>
+    <row r="354" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A354" s="2">
         <v>135428968</v>
       </c>
@@ -16053,11 +15575,9 @@
       <c r="K354" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="L354" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="355" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L354"/>
+    </row>
+    <row r="355" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A355" s="2">
         <v>135429144</v>
       </c>
@@ -16091,11 +15611,9 @@
       <c r="K355" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="L355" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="356" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L355"/>
+    </row>
+    <row r="356" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A356" s="2">
         <v>135429321</v>
       </c>
@@ -16129,11 +15647,9 @@
       <c r="K356" s="3" t="s">
         <v>368</v>
       </c>
-      <c r="L356" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="357" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L356"/>
+    </row>
+    <row r="357" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A357" s="2">
         <v>135429325</v>
       </c>
@@ -16167,11 +15683,9 @@
       <c r="K357" s="3" t="s">
         <v>369</v>
       </c>
-      <c r="L357" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="358" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L357"/>
+    </row>
+    <row r="358" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A358" s="2">
         <v>135429396</v>
       </c>
@@ -16205,11 +15719,9 @@
       <c r="K358" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="L358" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="359" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L358"/>
+    </row>
+    <row r="359" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A359" s="2">
         <v>135429461</v>
       </c>
@@ -16243,11 +15755,9 @@
       <c r="K359" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="L359" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="360" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L359"/>
+    </row>
+    <row r="360" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A360" s="2">
         <v>135429784</v>
       </c>
@@ -16281,11 +15791,9 @@
       <c r="K360" s="3" t="s">
         <v>372</v>
       </c>
-      <c r="L360" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="361" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L360"/>
+    </row>
+    <row r="361" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A361" s="2">
         <v>135430000</v>
       </c>
@@ -16319,11 +15827,9 @@
       <c r="K361" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="L361" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="362" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L361"/>
+    </row>
+    <row r="362" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A362" s="2">
         <v>135430187</v>
       </c>
@@ -16357,11 +15863,9 @@
       <c r="K362" s="3" t="s">
         <v>374</v>
       </c>
-      <c r="L362" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="363" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L362"/>
+    </row>
+    <row r="363" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A363" s="2">
         <v>135430437</v>
       </c>
@@ -16395,11 +15899,9 @@
       <c r="K363" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="L363" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="364" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L363"/>
+    </row>
+    <row r="364" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A364" s="2">
         <v>135431038</v>
       </c>
@@ -16433,11 +15935,9 @@
       <c r="K364" s="3" t="s">
         <v>376</v>
       </c>
-      <c r="L364" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="365" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L364"/>
+    </row>
+    <row r="365" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A365" s="2">
         <v>135431216</v>
       </c>
@@ -16471,11 +15971,9 @@
       <c r="K365" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="L365" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="366" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L365"/>
+    </row>
+    <row r="366" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A366" s="2">
         <v>135431275</v>
       </c>
@@ -16509,11 +16007,9 @@
       <c r="K366" s="3" t="s">
         <v>378</v>
       </c>
-      <c r="L366" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="367" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L366"/>
+    </row>
+    <row r="367" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A367" s="2">
         <v>135431525</v>
       </c>
@@ -16547,11 +16043,9 @@
       <c r="K367" s="3" t="s">
         <v>379</v>
       </c>
-      <c r="L367" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="368" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L367"/>
+    </row>
+    <row r="368" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A368" s="2">
         <v>135431664</v>
       </c>
@@ -16585,11 +16079,9 @@
       <c r="K368" s="3" t="s">
         <v>380</v>
       </c>
-      <c r="L368" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="369" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L368"/>
+    </row>
+    <row r="369" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A369" s="2">
         <v>135431969</v>
       </c>
@@ -16623,11 +16115,9 @@
       <c r="K369" s="3" t="s">
         <v>381</v>
       </c>
-      <c r="L369" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="370" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L369"/>
+    </row>
+    <row r="370" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A370" s="2">
         <v>135432019</v>
       </c>
@@ -16661,11 +16151,9 @@
       <c r="K370" s="3" t="s">
         <v>382</v>
       </c>
-      <c r="L370" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="371" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L370"/>
+    </row>
+    <row r="371" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A371" s="2">
         <v>135432188</v>
       </c>
@@ -16699,11 +16187,9 @@
       <c r="K371" s="3" t="s">
         <v>383</v>
       </c>
-      <c r="L371" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="372" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L371"/>
+    </row>
+    <row r="372" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A372" s="2">
         <v>135432308</v>
       </c>
@@ -16737,11 +16223,9 @@
       <c r="K372" s="3" t="s">
         <v>384</v>
       </c>
-      <c r="L372" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="373" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L372"/>
+    </row>
+    <row r="373" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A373" s="2">
         <v>135432745</v>
       </c>
@@ -16775,11 +16259,9 @@
       <c r="K373" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="L373" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="374" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L373"/>
+    </row>
+    <row r="374" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A374" s="2">
         <v>135432814</v>
       </c>
@@ -16813,11 +16295,9 @@
       <c r="K374" s="3" t="s">
         <v>386</v>
       </c>
-      <c r="L374" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="375" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L374"/>
+    </row>
+    <row r="375" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A375" s="2">
         <v>135433254</v>
       </c>
@@ -16851,11 +16331,9 @@
       <c r="K375" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="L375" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="376" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L375"/>
+    </row>
+    <row r="376" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A376" s="2">
         <v>135433438</v>
       </c>
@@ -16889,11 +16367,9 @@
       <c r="K376" s="3" t="s">
         <v>388</v>
       </c>
-      <c r="L376" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="377" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L376"/>
+    </row>
+    <row r="377" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A377" s="2">
         <v>133339612</v>
       </c>
@@ -16927,11 +16403,9 @@
       <c r="K377" s="3" t="s">
         <v>389</v>
       </c>
-      <c r="L377" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="378" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L377"/>
+    </row>
+    <row r="378" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A378" s="2">
         <v>135265136</v>
       </c>
@@ -16965,11 +16439,9 @@
       <c r="K378" s="3" t="s">
         <v>390</v>
       </c>
-      <c r="L378" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="379" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L378"/>
+    </row>
+    <row r="379" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A379" s="2">
         <v>135266692</v>
       </c>
@@ -17003,11 +16475,9 @@
       <c r="K379" s="3" t="s">
         <v>391</v>
       </c>
-      <c r="L379" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="380" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L379"/>
+    </row>
+    <row r="380" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A380" s="2">
         <v>132902606</v>
       </c>
@@ -17041,11 +16511,9 @@
       <c r="K380" s="3" t="s">
         <v>392</v>
       </c>
-      <c r="L380" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="381" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L380"/>
+    </row>
+    <row r="381" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A381" s="2">
         <v>133021163</v>
       </c>
@@ -17079,11 +16547,9 @@
       <c r="K381" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="L381" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="382" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L381"/>
+    </row>
+    <row r="382" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A382" s="2">
         <v>133533736</v>
       </c>
@@ -17117,11 +16583,9 @@
       <c r="K382" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="L382" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="383" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L382"/>
+    </row>
+    <row r="383" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A383" s="2">
         <v>134957478</v>
       </c>
@@ -17155,11 +16619,9 @@
       <c r="K383" s="3" t="s">
         <v>395</v>
       </c>
-      <c r="L383" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="384" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L383"/>
+    </row>
+    <row r="384" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A384" s="2">
         <v>135033285</v>
       </c>
@@ -17193,11 +16655,9 @@
       <c r="K384" s="3" t="s">
         <v>396</v>
       </c>
-      <c r="L384" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="385" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L384"/>
+    </row>
+    <row r="385" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A385" s="2">
         <v>135396502</v>
       </c>
@@ -17231,11 +16691,9 @@
       <c r="K385" s="3" t="s">
         <v>397</v>
       </c>
-      <c r="L385" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="386" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L385"/>
+    </row>
+    <row r="386" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A386" s="2">
         <v>135398130</v>
       </c>
@@ -17269,11 +16727,9 @@
       <c r="K386" s="3" t="s">
         <v>398</v>
       </c>
-      <c r="L386" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="387" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L386"/>
+    </row>
+    <row r="387" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A387" s="2">
         <v>130777969</v>
       </c>
@@ -17307,11 +16763,9 @@
       <c r="K387" s="3" t="s">
         <v>399</v>
       </c>
-      <c r="L387" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="388" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L387"/>
+    </row>
+    <row r="388" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A388" s="2">
         <v>131192846</v>
       </c>
@@ -17345,11 +16799,9 @@
       <c r="K388" s="3" t="s">
         <v>400</v>
       </c>
-      <c r="L388" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="389" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L388"/>
+    </row>
+    <row r="389" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A389" s="2">
         <v>131269670</v>
       </c>
@@ -17383,11 +16835,9 @@
       <c r="K389" s="3" t="s">
         <v>401</v>
       </c>
-      <c r="L389" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="390" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L389"/>
+    </row>
+    <row r="390" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A390" s="2">
         <v>131281698</v>
       </c>
@@ -17421,11 +16871,9 @@
       <c r="K390" s="3" t="s">
         <v>402</v>
       </c>
-      <c r="L390" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="391" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L390"/>
+    </row>
+    <row r="391" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A391" s="2">
         <v>131570357</v>
       </c>
@@ -17459,11 +16907,9 @@
       <c r="K391" s="3" t="s">
         <v>403</v>
       </c>
-      <c r="L391" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="392" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L391"/>
+    </row>
+    <row r="392" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A392" s="2">
         <v>131645204</v>
       </c>
@@ -17497,11 +16943,9 @@
       <c r="K392" s="3" t="s">
         <v>404</v>
       </c>
-      <c r="L392" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="393" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L392"/>
+    </row>
+    <row r="393" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A393" s="2">
         <v>131670888</v>
       </c>
@@ -17535,11 +16979,9 @@
       <c r="K393" s="3" t="s">
         <v>405</v>
       </c>
-      <c r="L393" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="394" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L393"/>
+    </row>
+    <row r="394" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A394" s="2">
         <v>131813044</v>
       </c>
@@ -17573,11 +17015,9 @@
       <c r="K394" s="3" t="s">
         <v>406</v>
       </c>
-      <c r="L394" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="395" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L394"/>
+    </row>
+    <row r="395" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A395" s="2">
         <v>131832415</v>
       </c>
@@ -17611,11 +17051,9 @@
       <c r="K395" s="3" t="s">
         <v>407</v>
       </c>
-      <c r="L395" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="396" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L395"/>
+    </row>
+    <row r="396" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A396" s="2">
         <v>132019460</v>
       </c>
@@ -17649,11 +17087,9 @@
       <c r="K396" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="L396" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="397" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L396"/>
+    </row>
+    <row r="397" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A397" s="2">
         <v>132346348</v>
       </c>
@@ -17687,11 +17123,9 @@
       <c r="K397" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="L397" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="398" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L397"/>
+    </row>
+    <row r="398" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A398" s="2">
         <v>132350788</v>
       </c>
@@ -17725,11 +17159,9 @@
       <c r="K398" s="3" t="s">
         <v>410</v>
       </c>
-      <c r="L398" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="399" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L398"/>
+    </row>
+    <row r="399" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A399" s="2">
         <v>132360757</v>
       </c>
@@ -17763,11 +17195,9 @@
       <c r="K399" s="3" t="s">
         <v>411</v>
       </c>
-      <c r="L399" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="400" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L399"/>
+    </row>
+    <row r="400" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A400" s="2">
         <v>132441246</v>
       </c>
@@ -17801,11 +17231,9 @@
       <c r="K400" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="L400" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="401" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L400"/>
+    </row>
+    <row r="401" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A401" s="2">
         <v>132546569</v>
       </c>
@@ -17839,11 +17267,9 @@
       <c r="K401" s="3" t="s">
         <v>413</v>
       </c>
-      <c r="L401" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="402" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L401"/>
+    </row>
+    <row r="402" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A402" s="2">
         <v>132572158</v>
       </c>
@@ -17877,11 +17303,9 @@
       <c r="K402" s="3" t="s">
         <v>414</v>
       </c>
-      <c r="L402" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="403" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L402"/>
+    </row>
+    <row r="403" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A403" s="2">
         <v>132576941</v>
       </c>
@@ -17915,11 +17339,9 @@
       <c r="K403" s="3" t="s">
         <v>415</v>
       </c>
-      <c r="L403" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="404" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L403"/>
+    </row>
+    <row r="404" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A404" s="2">
         <v>132578331</v>
       </c>
@@ -17953,11 +17375,9 @@
       <c r="K404" s="3" t="s">
         <v>416</v>
       </c>
-      <c r="L404" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="405" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L404"/>
+    </row>
+    <row r="405" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A405" s="2">
         <v>132582597</v>
       </c>
@@ -17991,11 +17411,9 @@
       <c r="K405" s="3" t="s">
         <v>417</v>
       </c>
-      <c r="L405" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="406" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L405"/>
+    </row>
+    <row r="406" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A406" s="2">
         <v>132584726</v>
       </c>
@@ -18029,11 +17447,9 @@
       <c r="K406" s="3" t="s">
         <v>418</v>
       </c>
-      <c r="L406" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="407" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L406"/>
+    </row>
+    <row r="407" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A407" s="2">
         <v>132780057</v>
       </c>
@@ -18067,11 +17483,9 @@
       <c r="K407" s="3" t="s">
         <v>419</v>
       </c>
-      <c r="L407" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="408" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L407"/>
+    </row>
+    <row r="408" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A408" s="2">
         <v>132790259</v>
       </c>
@@ -18105,11 +17519,9 @@
       <c r="K408" s="3" t="s">
         <v>420</v>
       </c>
-      <c r="L408" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="409" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L408"/>
+    </row>
+    <row r="409" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A409" s="2">
         <v>132851406</v>
       </c>
@@ -18143,11 +17555,9 @@
       <c r="K409" s="3" t="s">
         <v>421</v>
       </c>
-      <c r="L409" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="410" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L409"/>
+    </row>
+    <row r="410" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A410" s="2">
         <v>133024488</v>
       </c>
@@ -18181,11 +17591,9 @@
       <c r="K410" s="3" t="s">
         <v>422</v>
       </c>
-      <c r="L410" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="411" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L410"/>
+    </row>
+    <row r="411" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A411" s="2">
         <v>133215593</v>
       </c>
@@ -18219,11 +17627,9 @@
       <c r="K411" s="3" t="s">
         <v>423</v>
       </c>
-      <c r="L411" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="412" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L411"/>
+    </row>
+    <row r="412" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A412" s="2">
         <v>133244010</v>
       </c>
@@ -18257,11 +17663,9 @@
       <c r="K412" s="3" t="s">
         <v>424</v>
       </c>
-      <c r="L412" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="413" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L412"/>
+    </row>
+    <row r="413" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A413" s="2">
         <v>133250445</v>
       </c>
@@ -18295,11 +17699,9 @@
       <c r="K413" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="L413" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="414" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L413"/>
+    </row>
+    <row r="414" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A414" s="2">
         <v>133277960</v>
       </c>
@@ -18333,11 +17735,9 @@
       <c r="K414" s="3" t="s">
         <v>426</v>
       </c>
-      <c r="L414" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="415" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L414"/>
+    </row>
+    <row r="415" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A415" s="2">
         <v>133283003</v>
       </c>
@@ -18371,11 +17771,9 @@
       <c r="K415" s="3" t="s">
         <v>427</v>
       </c>
-      <c r="L415" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="416" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L415"/>
+    </row>
+    <row r="416" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A416" s="2">
         <v>133423941</v>
       </c>
@@ -18409,11 +17807,9 @@
       <c r="K416" s="3" t="s">
         <v>428</v>
       </c>
-      <c r="L416" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="417" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L416"/>
+    </row>
+    <row r="417" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A417" s="2">
         <v>133439960</v>
       </c>
@@ -18447,11 +17843,9 @@
       <c r="K417" s="3" t="s">
         <v>429</v>
       </c>
-      <c r="L417" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="418" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L417"/>
+    </row>
+    <row r="418" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A418" s="2">
         <v>133483658</v>
       </c>
@@ -18485,11 +17879,9 @@
       <c r="K418" s="3" t="s">
         <v>430</v>
       </c>
-      <c r="L418" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="419" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L418"/>
+    </row>
+    <row r="419" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A419" s="2">
         <v>133504678</v>
       </c>
@@ -18523,11 +17915,9 @@
       <c r="K419" s="3" t="s">
         <v>431</v>
       </c>
-      <c r="L419" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="420" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L419"/>
+    </row>
+    <row r="420" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A420" s="2">
         <v>133724684</v>
       </c>
@@ -18561,11 +17951,9 @@
       <c r="K420" s="3" t="s">
         <v>432</v>
       </c>
-      <c r="L420" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="421" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L420"/>
+    </row>
+    <row r="421" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A421" s="2">
         <v>133862028</v>
       </c>
@@ -18599,11 +17987,9 @@
       <c r="K421" s="3" t="s">
         <v>433</v>
       </c>
-      <c r="L421" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="422" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L421"/>
+    </row>
+    <row r="422" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A422" s="2">
         <v>133888778</v>
       </c>
@@ -18637,11 +18023,9 @@
       <c r="K422" s="3" t="s">
         <v>434</v>
       </c>
-      <c r="L422" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="423" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L422"/>
+    </row>
+    <row r="423" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A423" s="2">
         <v>133928108</v>
       </c>
@@ -18675,11 +18059,9 @@
       <c r="K423" s="3" t="s">
         <v>435</v>
       </c>
-      <c r="L423" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="424" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L423"/>
+    </row>
+    <row r="424" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A424" s="2">
         <v>133928773</v>
       </c>
@@ -18713,11 +18095,9 @@
       <c r="K424" s="3" t="s">
         <v>436</v>
       </c>
-      <c r="L424" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="425" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L424"/>
+    </row>
+    <row r="425" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A425" s="2">
         <v>134095759</v>
       </c>
@@ -18751,11 +18131,9 @@
       <c r="K425" s="3" t="s">
         <v>437</v>
       </c>
-      <c r="L425" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="426" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L425"/>
+    </row>
+    <row r="426" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A426" s="2">
         <v>134097371</v>
       </c>
@@ -18789,11 +18167,9 @@
       <c r="K426" s="3" t="s">
         <v>438</v>
       </c>
-      <c r="L426" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="427" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L426"/>
+    </row>
+    <row r="427" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A427" s="2">
         <v>134160091</v>
       </c>
@@ -18827,11 +18203,9 @@
       <c r="K427" s="3" t="s">
         <v>439</v>
       </c>
-      <c r="L427" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="428" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L427"/>
+    </row>
+    <row r="428" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A428" s="2">
         <v>134198760</v>
       </c>
@@ -18865,11 +18239,9 @@
       <c r="K428" s="3" t="s">
         <v>440</v>
       </c>
-      <c r="L428" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="429" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L428"/>
+    </row>
+    <row r="429" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A429" s="2">
         <v>134268327</v>
       </c>
@@ -18904,7 +18276,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="430" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A430" s="2">
         <v>134286097</v>
       </c>
@@ -18939,7 +18311,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="431" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A431" s="2">
         <v>134304083</v>
       </c>
@@ -18974,7 +18346,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="432" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A432" s="2">
         <v>134406071</v>
       </c>
@@ -24861,73 +24233,73 @@
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule dxfId="0" priority="71" type="duplicateValues"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="71"/>
   </conditionalFormatting>
-  <pageMargins bottom="0.78740157499999996" footer="0.31496062000000002" header="0.31496062000000002" left="0.511811024" right="0.511811024" top="0.78740157499999996"/>
-  <pageSetup orientation="portrait" paperSize="9" r:id="rId1"/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter>
-    <oddFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FPÚBLICO]]></oddFooter>
-    <evenFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FPÚBLICO]]></evenFooter>
-    <firstFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FPÚBLICO]]></firstFooter>
+    <oddFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FPÚBLICO</oddFooter>
+    <evenFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FPÚBLICO</evenFooter>
+    <firstFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FPÚBLICO</firstFooter>
   </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3317CFC-26C3-4764-9E25-62442657C783}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3317CFC-26C3-4764-9E25-62442657C783}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
-  <pageMargins bottom="0.78740157499999996" footer="0.31496062000000002" header="0.31496062000000002" left="0.511811024" right="0.511811024" top="0.78740157499999996"/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Planilha3">
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
-  <pageMargins bottom="0.78740157499999996" footer="0.31496062000000002" header="0.31496062000000002" left="0.511811024" right="0.511811024" top="0.78740157499999996"/>
-  <pageSetup orientation="portrait" paperSize="9" r:id="rId1"/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter>
-    <oddFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FPÚBLICO]]></oddFooter>
-    <evenFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FPÚBLICO]]></evenFooter>
-    <firstFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FPÚBLICO]]></firstFooter>
+    <oddFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FPÚBLICO</oddFooter>
+    <evenFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FPÚBLICO</evenFooter>
+    <firstFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FPÚBLICO</firstFooter>
   </headerFooter>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
+  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTAxOTQ2PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MjgvMDUvMjAxOSAxNzoxNTowNTwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAyOC8wNS8yMDE5ICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
-  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB274C4F-D882-4147-9885-1FF717648542}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DCA74A62-E908-4C3E-A1D4-6DC1121C84E7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB274C4F-D882-4147-9885-1FF717648542}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/erro/PendenciaGOInspecao.xlsx
+++ b/Treinamento/erro/PendenciaGOInspecao.xlsx
@@ -1,28 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr codeName="EstaPastaDeTrabalho"/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\erro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{78CA2DB2-332B-4E96-9392-EFE6578B68D2}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8CD409F-975C-4C19-9164-300A2F2BEEA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="11160" windowWidth="20730" xWindow="-120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}" yWindow="-120"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="envioPendenciaGOInspecao" r:id="rId1" sheetId="7"/>
-    <sheet name="17.03 P1" r:id="rId2" sheetId="9"/>
-    <sheet name="Planilha1" r:id="rId3" sheetId="8" state="hidden"/>
+    <sheet name="envioPendenciaGOInspecao" sheetId="7" r:id="rId1"/>
+    <sheet name="17.03 P1" sheetId="9" r:id="rId2"/>
+    <sheet name="Planilha1" sheetId="8" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">envioPendenciaGOInspecao!$A$1:$M$135</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">envioPendenciaGOInspecao!$A$1:$M$135</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20628" uniqueCount="747">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2641" uniqueCount="746">
   <si>
     <t>NR PROPOSTA</t>
   </si>
@@ -2265,9 +2265,6 @@
     <t>722   (Nota)
 CASA DE MADEIRA BE53298     Privado
   27/11/2025</t>
-  </si>
-  <si>
-    <t>Alerta:</t>
   </si>
   <si>
     <t>761   (Nota)
@@ -2334,7 +2331,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -2396,34 +2392,34 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="8">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
-    <xf applyAlignment="1" applyFill="1" applyFont="1" borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" applyFill="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="14" xfId="0">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="1">
     <dxf>
@@ -2434,7 +2430,7 @@
       </fill>
     </dxf>
   </dxfs>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -2447,7 +2443,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
@@ -2548,7 +2544,7 @@
         </a:fontRef>
       </xdr:style>
       <xdr:txBody>
-        <a:bodyPr anchor="t" horzOverflow="clip" rtlCol="0" vertOverflow="clip"/>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
@@ -2589,7 +2585,7 @@
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst>
-            <a:gd fmla="val 50000" name="adj1"/>
+            <a:gd name="adj1" fmla="val 50000"/>
           </a:avLst>
         </a:prstGeom>
         <a:ln>
@@ -2663,7 +2659,7 @@
         </a:fontRef>
       </xdr:style>
       <xdr:txBody>
-        <a:bodyPr anchor="t" horzOverflow="clip" rtlCol="0" vertOverflow="clip"/>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
@@ -2672,7 +2668,7 @@
             <a:t>Usaremos este campo para informar qual nota será utilizada.</a:t>
           </a:r>
           <a:r>
-            <a:rPr baseline="0" lang="pt-BR" sz="1100"/>
+            <a:rPr lang="pt-BR" sz="1100" baseline="0"/>
             <a:t> Todo o fluxo continua sem alteração &gt; Pega a Proposta na coluna "A" e vai até a FG na plataforma, na lateral em Nota/Agenda utilizará a nota informada na coluna "I".</a:t>
           </a:r>
           <a:endParaRPr lang="pt-BR" sz="1100"/>
@@ -2689,10 +2685,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -2890,21 +2886,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="6350">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -2921,7 +2917,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -2973,33 +2969,33 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" name="Office Theme" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Planilha1">
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:M709"/>
+  <dimension ref="A1:L709"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="2" width="23.28515625" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" style="2" width="13.7109375" collapsed="true"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="2" width="6.7109375" collapsed="true"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="2" width="15.5703125" collapsed="true"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="2" width="22.0" collapsed="true"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="2" width="14.85546875" collapsed="true"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="2" width="10.28515625" collapsed="true"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="2" width="12.42578125" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" style="2" width="12.42578125" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="2" width="15.85546875" collapsed="true"/>
-    <col min="11" max="11" style="2" width="9.140625" collapsed="true"/>
-    <col min="12" max="12" customWidth="true" style="7" width="85.7109375" collapsed="true"/>
-    <col min="13" max="16384" style="2" width="9.140625" collapsed="true"/>
+    <col min="1" max="1" width="23.28515625" style="2" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="13.7109375" style="2" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="6.7109375" style="2" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="15.5703125" style="2" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="22" style="2" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="14.85546875" style="2" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="10.28515625" style="2" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="12.42578125" style="2" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="12.42578125" style="2" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="15.85546875" style="2" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="9.140625" style="2" collapsed="1"/>
+    <col min="12" max="12" width="85.7109375" style="7" customWidth="1" collapsed="1"/>
+    <col min="13" max="16384" width="9.140625" style="2" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -3040,7 +3036,7 @@
         <v>147</v>
       </c>
     </row>
-    <row customFormat="1" r="2" s="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>135213285</v>
       </c>
@@ -3078,7 +3074,7 @@
         <v>723</v>
       </c>
     </row>
-    <row customHeight="1" ht="16.5" r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>135473483</v>
       </c>
@@ -12119,7 +12115,7 @@
         <v>252</v>
       </c>
       <c r="L240" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="241" spans="1:12" x14ac:dyDescent="0.25">
@@ -12157,7 +12153,7 @@
         <v>253</v>
       </c>
       <c r="L241" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="242" spans="1:12" x14ac:dyDescent="0.25">
@@ -12195,7 +12191,7 @@
         <v>254</v>
       </c>
       <c r="L242" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="243" spans="1:12" x14ac:dyDescent="0.25">
@@ -12233,7 +12229,7 @@
         <v>255</v>
       </c>
       <c r="L243" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="244" spans="1:12" x14ac:dyDescent="0.25">
@@ -12271,7 +12267,7 @@
         <v>256</v>
       </c>
       <c r="L244" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="245" spans="1:12" x14ac:dyDescent="0.25">
@@ -12309,7 +12305,7 @@
         <v>257</v>
       </c>
       <c r="L245" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="246" spans="1:12" x14ac:dyDescent="0.25">
@@ -12347,7 +12343,7 @@
         <v>258</v>
       </c>
       <c r="L246" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="247" spans="1:12" x14ac:dyDescent="0.25">
@@ -12385,7 +12381,7 @@
         <v>259</v>
       </c>
       <c r="L247" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="248" spans="1:12" x14ac:dyDescent="0.25">
@@ -12423,7 +12419,7 @@
         <v>260</v>
       </c>
       <c r="L248" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="249" spans="1:12" x14ac:dyDescent="0.25">
@@ -12461,7 +12457,7 @@
         <v>261</v>
       </c>
       <c r="L249" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="250" spans="1:12" x14ac:dyDescent="0.25">
@@ -12499,7 +12495,7 @@
         <v>262</v>
       </c>
       <c r="L250" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="251" spans="1:12" x14ac:dyDescent="0.25">
@@ -12537,7 +12533,7 @@
         <v>263</v>
       </c>
       <c r="L251" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="252" spans="1:12" x14ac:dyDescent="0.25">
@@ -12575,7 +12571,7 @@
         <v>264</v>
       </c>
       <c r="L252" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="253" spans="1:12" x14ac:dyDescent="0.25">
@@ -12613,7 +12609,7 @@
         <v>265</v>
       </c>
       <c r="L253" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="254" spans="1:12" x14ac:dyDescent="0.25">
@@ -12651,7 +12647,7 @@
         <v>266</v>
       </c>
       <c r="L254" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="255" spans="1:12" x14ac:dyDescent="0.25">
@@ -12689,7 +12685,7 @@
         <v>267</v>
       </c>
       <c r="L255" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="256" spans="1:12" x14ac:dyDescent="0.25">
@@ -12727,7 +12723,7 @@
         <v>268</v>
       </c>
       <c r="L256" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="257" spans="1:12" x14ac:dyDescent="0.25">
@@ -12765,7 +12761,7 @@
         <v>269</v>
       </c>
       <c r="L257" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="258" spans="1:12" x14ac:dyDescent="0.25">
@@ -12803,7 +12799,7 @@
         <v>270</v>
       </c>
       <c r="L258" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="259" spans="1:12" x14ac:dyDescent="0.25">
@@ -12841,7 +12837,7 @@
         <v>271</v>
       </c>
       <c r="L259" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="260" spans="1:12" x14ac:dyDescent="0.25">
@@ -12879,7 +12875,7 @@
         <v>272</v>
       </c>
       <c r="L260" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="261" spans="1:12" x14ac:dyDescent="0.25">
@@ -12917,7 +12913,7 @@
         <v>273</v>
       </c>
       <c r="L261" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="262" spans="1:12" x14ac:dyDescent="0.25">
@@ -12955,7 +12951,7 @@
         <v>274</v>
       </c>
       <c r="L262" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="263" spans="1:12" x14ac:dyDescent="0.25">
@@ -12993,7 +12989,7 @@
         <v>275</v>
       </c>
       <c r="L263" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="264" spans="1:12" x14ac:dyDescent="0.25">
@@ -13031,7 +13027,7 @@
         <v>276</v>
       </c>
       <c r="L264" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="265" spans="1:12" x14ac:dyDescent="0.25">
@@ -13069,7 +13065,7 @@
         <v>277</v>
       </c>
       <c r="L265" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="266" spans="1:12" x14ac:dyDescent="0.25">
@@ -13107,7 +13103,7 @@
         <v>278</v>
       </c>
       <c r="L266" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="267" spans="1:12" x14ac:dyDescent="0.25">
@@ -13145,7 +13141,7 @@
         <v>279</v>
       </c>
       <c r="L267" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="268" spans="1:12" x14ac:dyDescent="0.25">
@@ -13183,7 +13179,7 @@
         <v>280</v>
       </c>
       <c r="L268" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="269" spans="1:12" x14ac:dyDescent="0.25">
@@ -13221,7 +13217,7 @@
         <v>281</v>
       </c>
       <c r="L269" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="270" spans="1:12" x14ac:dyDescent="0.25">
@@ -13259,7 +13255,7 @@
         <v>282</v>
       </c>
       <c r="L270" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="271" spans="1:12" x14ac:dyDescent="0.25">
@@ -13297,7 +13293,7 @@
         <v>283</v>
       </c>
       <c r="L271" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="272" spans="1:12" x14ac:dyDescent="0.25">
@@ -13335,7 +13331,7 @@
         <v>284</v>
       </c>
       <c r="L272" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="273" spans="1:12" x14ac:dyDescent="0.25">
@@ -13373,7 +13369,7 @@
         <v>285</v>
       </c>
       <c r="L273" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="274" spans="1:12" x14ac:dyDescent="0.25">
@@ -13411,7 +13407,7 @@
         <v>286</v>
       </c>
       <c r="L274" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="275" spans="1:12" x14ac:dyDescent="0.25">
@@ -13449,7 +13445,7 @@
         <v>287</v>
       </c>
       <c r="L275" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="276" spans="1:12" x14ac:dyDescent="0.25">
@@ -13487,7 +13483,7 @@
         <v>288</v>
       </c>
       <c r="L276" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="277" spans="1:12" x14ac:dyDescent="0.25">
@@ -13525,7 +13521,7 @@
         <v>289</v>
       </c>
       <c r="L277" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="278" spans="1:12" x14ac:dyDescent="0.25">
@@ -13563,7 +13559,7 @@
         <v>290</v>
       </c>
       <c r="L278" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="279" spans="1:12" x14ac:dyDescent="0.25">
@@ -13601,7 +13597,7 @@
         <v>291</v>
       </c>
       <c r="L279" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="280" spans="1:12" x14ac:dyDescent="0.25">
@@ -13639,7 +13635,7 @@
         <v>292</v>
       </c>
       <c r="L280" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="281" spans="1:12" x14ac:dyDescent="0.25">
@@ -13677,7 +13673,7 @@
         <v>293</v>
       </c>
       <c r="L281" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="282" spans="1:12" x14ac:dyDescent="0.25">
@@ -13715,7 +13711,7 @@
         <v>294</v>
       </c>
       <c r="L282" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="283" spans="1:12" x14ac:dyDescent="0.25">
@@ -13753,7 +13749,7 @@
         <v>295</v>
       </c>
       <c r="L283" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="284" spans="1:12" x14ac:dyDescent="0.25">
@@ -13791,7 +13787,7 @@
         <v>296</v>
       </c>
       <c r="L284" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="285" spans="1:12" x14ac:dyDescent="0.25">
@@ -13829,7 +13825,7 @@
         <v>297</v>
       </c>
       <c r="L285" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="286" spans="1:12" x14ac:dyDescent="0.25">
@@ -13867,7 +13863,7 @@
         <v>298</v>
       </c>
       <c r="L286" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="287" spans="1:12" x14ac:dyDescent="0.25">
@@ -13905,7 +13901,7 @@
         <v>299</v>
       </c>
       <c r="L287" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="288" spans="1:12" x14ac:dyDescent="0.25">
@@ -13943,7 +13939,7 @@
         <v>300</v>
       </c>
       <c r="L288" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="289" spans="1:12" x14ac:dyDescent="0.25">
@@ -13981,7 +13977,7 @@
         <v>301</v>
       </c>
       <c r="L289" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="290" spans="1:12" x14ac:dyDescent="0.25">
@@ -14019,7 +14015,7 @@
         <v>302</v>
       </c>
       <c r="L290" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="291" spans="1:12" x14ac:dyDescent="0.25">
@@ -14057,7 +14053,7 @@
         <v>303</v>
       </c>
       <c r="L291" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="292" spans="1:12" x14ac:dyDescent="0.25">
@@ -14095,7 +14091,7 @@
         <v>304</v>
       </c>
       <c r="L292" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="293" spans="1:12" x14ac:dyDescent="0.25">
@@ -14133,7 +14129,7 @@
         <v>305</v>
       </c>
       <c r="L293" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="294" spans="1:12" x14ac:dyDescent="0.25">
@@ -14171,7 +14167,7 @@
         <v>306</v>
       </c>
       <c r="L294" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="295" spans="1:12" x14ac:dyDescent="0.25">
@@ -14209,7 +14205,7 @@
         <v>307</v>
       </c>
       <c r="L295" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="296" spans="1:12" x14ac:dyDescent="0.25">
@@ -14247,7 +14243,7 @@
         <v>308</v>
       </c>
       <c r="L296" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="297" spans="1:12" x14ac:dyDescent="0.25">
@@ -14285,7 +14281,7 @@
         <v>309</v>
       </c>
       <c r="L297" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="298" spans="1:12" x14ac:dyDescent="0.25">
@@ -14323,7 +14319,7 @@
         <v>310</v>
       </c>
       <c r="L298" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="299" spans="1:12" x14ac:dyDescent="0.25">
@@ -14361,7 +14357,7 @@
         <v>311</v>
       </c>
       <c r="L299" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="300" spans="1:12" x14ac:dyDescent="0.25">
@@ -14399,7 +14395,7 @@
         <v>312</v>
       </c>
       <c r="L300" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="301" spans="1:12" x14ac:dyDescent="0.25">
@@ -14437,7 +14433,7 @@
         <v>313</v>
       </c>
       <c r="L301" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="302" spans="1:12" x14ac:dyDescent="0.25">
@@ -14475,7 +14471,7 @@
         <v>314</v>
       </c>
       <c r="L302" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="303" spans="1:12" x14ac:dyDescent="0.25">
@@ -14513,7 +14509,7 @@
         <v>315</v>
       </c>
       <c r="L303" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="304" spans="1:12" x14ac:dyDescent="0.25">
@@ -14551,10 +14547,10 @@
         <v>316</v>
       </c>
       <c r="L304" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="305" spans="1:11" x14ac:dyDescent="0.25">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="305" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A305" s="2">
         <v>135546070</v>
       </c>
@@ -14589,10 +14585,10 @@
         <v>317</v>
       </c>
       <c r="L305" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="306" spans="1:11" x14ac:dyDescent="0.25">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="306" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A306" s="2">
         <v>135546104</v>
       </c>
@@ -14627,10 +14623,10 @@
         <v>318</v>
       </c>
       <c r="L306" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="307" spans="1:11" x14ac:dyDescent="0.25">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="307" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A307" s="2">
         <v>135546116</v>
       </c>
@@ -14665,10 +14661,10 @@
         <v>319</v>
       </c>
       <c r="L307" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="308" spans="1:11" x14ac:dyDescent="0.25">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="308" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A308" s="2">
         <v>135546134</v>
       </c>
@@ -14703,10 +14699,10 @@
         <v>320</v>
       </c>
       <c r="L308" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="309" spans="1:11" x14ac:dyDescent="0.25">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="309" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A309" s="2">
         <v>135546166</v>
       </c>
@@ -14741,10 +14737,10 @@
         <v>321</v>
       </c>
       <c r="L309" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="310" spans="1:11" x14ac:dyDescent="0.25">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="310" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A310" s="2">
         <v>135546181</v>
       </c>
@@ -14779,10 +14775,10 @@
         <v>322</v>
       </c>
       <c r="L310" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="311" spans="1:11" x14ac:dyDescent="0.25">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="311" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A311" s="2">
         <v>135546217</v>
       </c>
@@ -14817,10 +14813,10 @@
         <v>323</v>
       </c>
       <c r="L311" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="312" spans="1:11" x14ac:dyDescent="0.25">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="312" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A312" s="2">
         <v>135546370</v>
       </c>
@@ -14855,10 +14851,10 @@
         <v>324</v>
       </c>
       <c r="L312" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="313" spans="1:11" x14ac:dyDescent="0.25">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="313" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A313" s="2">
         <v>135546433</v>
       </c>
@@ -14893,10 +14889,10 @@
         <v>325</v>
       </c>
       <c r="L313" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="314" spans="1:11" x14ac:dyDescent="0.25">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="314" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A314" s="2">
         <v>135546551</v>
       </c>
@@ -14931,10 +14927,10 @@
         <v>326</v>
       </c>
       <c r="L314" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="315" spans="1:11" x14ac:dyDescent="0.25">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="315" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A315" s="2">
         <v>135546632</v>
       </c>
@@ -14969,10 +14965,10 @@
         <v>327</v>
       </c>
       <c r="L315" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="316" spans="1:11" x14ac:dyDescent="0.25">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="316" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A316" s="2">
         <v>135546642</v>
       </c>
@@ -15007,10 +15003,10 @@
         <v>328</v>
       </c>
       <c r="L316" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="317" spans="1:11" x14ac:dyDescent="0.25">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="317" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A317" s="2">
         <v>135546671</v>
       </c>
@@ -15045,10 +15041,10 @@
         <v>329</v>
       </c>
       <c r="L317" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="318" spans="1:11" x14ac:dyDescent="0.25">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="318" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A318" s="2">
         <v>135546910</v>
       </c>
@@ -15083,10 +15079,10 @@
         <v>330</v>
       </c>
       <c r="L318" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="319" spans="1:11" x14ac:dyDescent="0.25">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="319" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A319" s="2">
         <v>135546925</v>
       </c>
@@ -15121,10 +15117,10 @@
         <v>331</v>
       </c>
       <c r="L319" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="320" spans="1:11" x14ac:dyDescent="0.25">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="320" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A320" s="2">
         <v>135546936</v>
       </c>
@@ -15159,10 +15155,10 @@
         <v>332</v>
       </c>
       <c r="L320" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="321" spans="1:11" x14ac:dyDescent="0.25">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="321" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A321" s="2">
         <v>135546978</v>
       </c>
@@ -15197,10 +15193,10 @@
         <v>333</v>
       </c>
       <c r="L321" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="322" spans="1:11" x14ac:dyDescent="0.25">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="322" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A322" s="2">
         <v>135547031</v>
       </c>
@@ -15235,10 +15231,10 @@
         <v>334</v>
       </c>
       <c r="L322" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="323" spans="1:11" x14ac:dyDescent="0.25">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="323" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A323" s="2">
         <v>135547067</v>
       </c>
@@ -15273,10 +15269,10 @@
         <v>335</v>
       </c>
       <c r="L323" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="324" spans="1:11" x14ac:dyDescent="0.25">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="324" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A324" s="2">
         <v>135547160</v>
       </c>
@@ -15311,10 +15307,10 @@
         <v>336</v>
       </c>
       <c r="L324" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="325" spans="1:11" x14ac:dyDescent="0.25">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="325" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A325" s="2">
         <v>135547249</v>
       </c>
@@ -15349,10 +15345,10 @@
         <v>337</v>
       </c>
       <c r="L325" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="326" spans="1:11" x14ac:dyDescent="0.25">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="326" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A326" s="2">
         <v>135547331</v>
       </c>
@@ -15387,10 +15383,10 @@
         <v>338</v>
       </c>
       <c r="L326" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="327" spans="1:11" x14ac:dyDescent="0.25">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="327" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A327" s="2">
         <v>135547378</v>
       </c>
@@ -15425,10 +15421,10 @@
         <v>339</v>
       </c>
       <c r="L327" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="328" spans="1:11" x14ac:dyDescent="0.25">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="328" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A328" s="2">
         <v>135547405</v>
       </c>
@@ -15463,10 +15459,10 @@
         <v>340</v>
       </c>
       <c r="L328" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="329" spans="1:11" x14ac:dyDescent="0.25">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="329" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A329" s="2">
         <v>135547623</v>
       </c>
@@ -15501,10 +15497,10 @@
         <v>341</v>
       </c>
       <c r="L329" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="330" spans="1:11" x14ac:dyDescent="0.25">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="330" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A330" s="2">
         <v>135547836</v>
       </c>
@@ -15539,10 +15535,10 @@
         <v>342</v>
       </c>
       <c r="L330" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="331" spans="1:11" x14ac:dyDescent="0.25">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="331" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A331" s="2">
         <v>135547940</v>
       </c>
@@ -15577,10 +15573,10 @@
         <v>343</v>
       </c>
       <c r="L331" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="332" spans="1:11" x14ac:dyDescent="0.25">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="332" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A332" s="2">
         <v>135548019</v>
       </c>
@@ -15615,10 +15611,10 @@
         <v>344</v>
       </c>
       <c r="L332" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="333" spans="1:11" x14ac:dyDescent="0.25">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="333" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A333" s="2">
         <v>135548208</v>
       </c>
@@ -15653,10 +15649,10 @@
         <v>345</v>
       </c>
       <c r="L333" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="334" spans="1:11" x14ac:dyDescent="0.25">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="334" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A334" s="2">
         <v>135548217</v>
       </c>
@@ -15691,10 +15687,10 @@
         <v>346</v>
       </c>
       <c r="L334" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="335" spans="1:11" x14ac:dyDescent="0.25">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="335" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A335" s="2">
         <v>135548304</v>
       </c>
@@ -15729,10 +15725,10 @@
         <v>347</v>
       </c>
       <c r="L335" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="336" spans="1:11" x14ac:dyDescent="0.25">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="336" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A336" s="2">
         <v>135548415</v>
       </c>
@@ -15767,10 +15763,10 @@
         <v>348</v>
       </c>
       <c r="L336" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="337" spans="1:11" x14ac:dyDescent="0.25">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="337" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A337" s="2">
         <v>135548763</v>
       </c>
@@ -15805,10 +15801,10 @@
         <v>349</v>
       </c>
       <c r="L337" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="338" spans="1:11" x14ac:dyDescent="0.25">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="338" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A338" s="2">
         <v>135548964</v>
       </c>
@@ -15843,10 +15839,10 @@
         <v>350</v>
       </c>
       <c r="L338" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="339" spans="1:11" x14ac:dyDescent="0.25">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="339" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A339" s="2">
         <v>135549241</v>
       </c>
@@ -15881,10 +15877,10 @@
         <v>351</v>
       </c>
       <c r="L339" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="340" spans="1:11" x14ac:dyDescent="0.25">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="340" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A340" s="2">
         <v>135549440</v>
       </c>
@@ -15919,10 +15915,10 @@
         <v>352</v>
       </c>
       <c r="L340" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="341" spans="1:11" x14ac:dyDescent="0.25">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="341" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A341" s="2">
         <v>135549488</v>
       </c>
@@ -15957,10 +15953,10 @@
         <v>353</v>
       </c>
       <c r="L341" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="342" spans="1:11" x14ac:dyDescent="0.25">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="342" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A342" s="2">
         <v>135549955</v>
       </c>
@@ -15995,10 +15991,10 @@
         <v>354</v>
       </c>
       <c r="L342" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="343" spans="1:11" x14ac:dyDescent="0.25">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="343" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A343" s="2">
         <v>135531198</v>
       </c>
@@ -16033,10 +16029,10 @@
         <v>355</v>
       </c>
       <c r="L343" t="s">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="344" spans="1:11" x14ac:dyDescent="0.25">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="344" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A344" s="2">
         <v>135535189</v>
       </c>
@@ -16071,10 +16067,10 @@
         <v>356</v>
       </c>
       <c r="L344" t="s">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="345" spans="1:11" x14ac:dyDescent="0.25">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="345" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A345" s="2">
         <v>132408495</v>
       </c>
@@ -16109,10 +16105,10 @@
         <v>357</v>
       </c>
       <c r="L345" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="346" spans="1:11" x14ac:dyDescent="0.25">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="346" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A346" s="2">
         <v>135174924</v>
       </c>
@@ -16147,10 +16143,10 @@
         <v>358</v>
       </c>
       <c r="L346" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="347" spans="1:11" x14ac:dyDescent="0.25">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="347" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A347" s="2">
         <v>135535836</v>
       </c>
@@ -16185,10 +16181,10 @@
         <v>359</v>
       </c>
       <c r="L347" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="348" spans="1:11" x14ac:dyDescent="0.25">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="348" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A348" s="2">
         <v>135543247</v>
       </c>
@@ -16223,10 +16219,10 @@
         <v>360</v>
       </c>
       <c r="L348" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="349" spans="1:11" x14ac:dyDescent="0.25">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="349" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A349" s="2">
         <v>132675340</v>
       </c>
@@ -16261,10 +16257,10 @@
         <v>361</v>
       </c>
       <c r="L349" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="350" spans="1:11" x14ac:dyDescent="0.25">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="350" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A350" s="2">
         <v>135448015</v>
       </c>
@@ -16299,10 +16295,10 @@
         <v>362</v>
       </c>
       <c r="L350" t="s">
-        <v>739</v>
-      </c>
-    </row>
-    <row r="351" spans="1:11" x14ac:dyDescent="0.25">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="351" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A351" s="2">
         <v>135454529</v>
       </c>
@@ -16337,10 +16333,10 @@
         <v>363</v>
       </c>
       <c r="L351" t="s">
-        <v>739</v>
-      </c>
-    </row>
-    <row r="352" spans="1:11" x14ac:dyDescent="0.25">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="352" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A352" s="2">
         <v>135457989</v>
       </c>
@@ -16375,10 +16371,10 @@
         <v>364</v>
       </c>
       <c r="L352" t="s">
-        <v>739</v>
-      </c>
-    </row>
-    <row r="353" spans="1:11" x14ac:dyDescent="0.25">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="353" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A353" s="2">
         <v>135462357</v>
       </c>
@@ -16413,10 +16409,10 @@
         <v>365</v>
       </c>
       <c r="L353" t="s">
-        <v>739</v>
-      </c>
-    </row>
-    <row r="354" spans="1:11" x14ac:dyDescent="0.25">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="354" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A354" s="2">
         <v>135478078</v>
       </c>
@@ -16451,10 +16447,10 @@
         <v>366</v>
       </c>
       <c r="L354" t="s">
-        <v>739</v>
-      </c>
-    </row>
-    <row r="355" spans="1:11" x14ac:dyDescent="0.25">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="355" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A355" s="2">
         <v>888212966</v>
       </c>
@@ -16489,10 +16485,10 @@
         <v>367</v>
       </c>
       <c r="L355" t="s">
-        <v>740</v>
-      </c>
-    </row>
-    <row r="356" spans="1:11" x14ac:dyDescent="0.25">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="356" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A356" s="2">
         <v>888212968</v>
       </c>
@@ -16527,10 +16523,10 @@
         <v>368</v>
       </c>
       <c r="L356" t="s">
-        <v>740</v>
-      </c>
-    </row>
-    <row r="357" spans="1:11" x14ac:dyDescent="0.25">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="357" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A357" s="2">
         <v>888212976</v>
       </c>
@@ -16565,10 +16561,10 @@
         <v>369</v>
       </c>
       <c r="L357" t="s">
-        <v>740</v>
-      </c>
-    </row>
-    <row r="358" spans="1:11" x14ac:dyDescent="0.25">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="358" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A358" s="2">
         <v>888212980</v>
       </c>
@@ -16603,10 +16599,10 @@
         <v>370</v>
       </c>
       <c r="L358" t="s">
-        <v>740</v>
-      </c>
-    </row>
-    <row r="359" spans="1:11" x14ac:dyDescent="0.25">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="359" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A359" s="2">
         <v>888212981</v>
       </c>
@@ -16641,10 +16637,10 @@
         <v>371</v>
       </c>
       <c r="L359" t="s">
-        <v>740</v>
-      </c>
-    </row>
-    <row r="360" spans="1:11" x14ac:dyDescent="0.25">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="360" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A360" s="2">
         <v>888212993</v>
       </c>
@@ -16679,10 +16675,10 @@
         <v>372</v>
       </c>
       <c r="L360" t="s">
-        <v>740</v>
-      </c>
-    </row>
-    <row r="361" spans="1:11" x14ac:dyDescent="0.25">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="361" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A361" s="2">
         <v>888212995</v>
       </c>
@@ -16717,10 +16713,10 @@
         <v>373</v>
       </c>
       <c r="L361" t="s">
-        <v>740</v>
-      </c>
-    </row>
-    <row r="362" spans="1:11" x14ac:dyDescent="0.25">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="362" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A362" s="2">
         <v>888213003</v>
       </c>
@@ -16755,10 +16751,10 @@
         <v>374</v>
       </c>
       <c r="L362" t="s">
-        <v>740</v>
-      </c>
-    </row>
-    <row r="363" spans="1:11" x14ac:dyDescent="0.25">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="363" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A363" s="2">
         <v>888213004</v>
       </c>
@@ -16793,10 +16789,10 @@
         <v>375</v>
       </c>
       <c r="L363" t="s">
-        <v>740</v>
-      </c>
-    </row>
-    <row r="364" spans="1:11" x14ac:dyDescent="0.25">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="364" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A364" s="2">
         <v>888213005</v>
       </c>
@@ -16831,10 +16827,10 @@
         <v>376</v>
       </c>
       <c r="L364" t="s">
-        <v>740</v>
-      </c>
-    </row>
-    <row r="365" spans="1:11" x14ac:dyDescent="0.25">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="365" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A365" s="2">
         <v>888213014</v>
       </c>
@@ -16869,10 +16865,10 @@
         <v>377</v>
       </c>
       <c r="L365" t="s">
-        <v>740</v>
-      </c>
-    </row>
-    <row r="366" spans="1:11" x14ac:dyDescent="0.25">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="366" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A366" s="2">
         <v>888213020</v>
       </c>
@@ -16907,10 +16903,10 @@
         <v>378</v>
       </c>
       <c r="L366" t="s">
-        <v>740</v>
-      </c>
-    </row>
-    <row r="367" spans="1:11" x14ac:dyDescent="0.25">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="367" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A367" s="2">
         <v>888213024</v>
       </c>
@@ -16945,10 +16941,10 @@
         <v>379</v>
       </c>
       <c r="L367" t="s">
-        <v>740</v>
-      </c>
-    </row>
-    <row r="368" spans="1:11" x14ac:dyDescent="0.25">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="368" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A368" s="2">
         <v>135528677</v>
       </c>
@@ -16983,10 +16979,10 @@
         <v>380</v>
       </c>
       <c r="L368" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="369" spans="1:11" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="369" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A369" s="2">
         <v>135528771</v>
       </c>
@@ -17021,10 +17017,10 @@
         <v>381</v>
       </c>
       <c r="L369" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="370" spans="1:11" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="370" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A370" s="2">
         <v>135528872</v>
       </c>
@@ -17059,10 +17055,10 @@
         <v>382</v>
       </c>
       <c r="L370" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="371" spans="1:11" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="371" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A371" s="2">
         <v>135529015</v>
       </c>
@@ -17097,10 +17093,10 @@
         <v>383</v>
       </c>
       <c r="L371" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="372" spans="1:11" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="372" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A372" s="2">
         <v>135529187</v>
       </c>
@@ -17135,10 +17131,10 @@
         <v>384</v>
       </c>
       <c r="L372" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="373" spans="1:11" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="373" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A373" s="2">
         <v>135530039</v>
       </c>
@@ -17173,10 +17169,10 @@
         <v>385</v>
       </c>
       <c r="L373" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="374" spans="1:11" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="374" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A374" s="2">
         <v>135530042</v>
       </c>
@@ -17211,10 +17207,10 @@
         <v>386</v>
       </c>
       <c r="L374" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="375" spans="1:11" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="375" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A375" s="2">
         <v>135530467</v>
       </c>
@@ -17249,10 +17245,10 @@
         <v>387</v>
       </c>
       <c r="L375" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="376" spans="1:11" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="376" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A376" s="2">
         <v>135530634</v>
       </c>
@@ -17287,10 +17283,10 @@
         <v>388</v>
       </c>
       <c r="L376" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="377" spans="1:11" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="377" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A377" s="2">
         <v>135530668</v>
       </c>
@@ -17325,10 +17321,10 @@
         <v>389</v>
       </c>
       <c r="L377" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="378" spans="1:11" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="378" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A378" s="2">
         <v>135530879</v>
       </c>
@@ -17363,10 +17359,10 @@
         <v>390</v>
       </c>
       <c r="L378" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="379" spans="1:11" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="379" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A379" s="2">
         <v>135531050</v>
       </c>
@@ -17401,10 +17397,10 @@
         <v>391</v>
       </c>
       <c r="L379" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="380" spans="1:11" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="380" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A380" s="2">
         <v>135531241</v>
       </c>
@@ -17439,10 +17435,10 @@
         <v>392</v>
       </c>
       <c r="L380" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="381" spans="1:11" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="381" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A381" s="2">
         <v>135531558</v>
       </c>
@@ -17477,10 +17473,10 @@
         <v>393</v>
       </c>
       <c r="L381" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="382" spans="1:11" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="382" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A382" s="2">
         <v>135531960</v>
       </c>
@@ -17515,10 +17511,10 @@
         <v>394</v>
       </c>
       <c r="L382" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="383" spans="1:11" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="383" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A383" s="2">
         <v>135531975</v>
       </c>
@@ -17553,10 +17549,10 @@
         <v>395</v>
       </c>
       <c r="L383" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="384" spans="1:11" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="384" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A384" s="2">
         <v>135532727</v>
       </c>
@@ -17591,10 +17587,10 @@
         <v>396</v>
       </c>
       <c r="L384" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="385" spans="1:11" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="385" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A385" s="2">
         <v>135532734</v>
       </c>
@@ -17629,10 +17625,10 @@
         <v>397</v>
       </c>
       <c r="L385" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="386" spans="1:11" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="386" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A386" s="2">
         <v>135532998</v>
       </c>
@@ -17667,10 +17663,10 @@
         <v>398</v>
       </c>
       <c r="L386" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="387" spans="1:11" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="387" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A387" s="2">
         <v>135533098</v>
       </c>
@@ -17705,10 +17701,10 @@
         <v>399</v>
       </c>
       <c r="L387" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="388" spans="1:11" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="388" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A388" s="2">
         <v>135533604</v>
       </c>
@@ -17743,10 +17739,10 @@
         <v>400</v>
       </c>
       <c r="L388" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="389" spans="1:11" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="389" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A389" s="2">
         <v>135533631</v>
       </c>
@@ -17781,10 +17777,10 @@
         <v>401</v>
       </c>
       <c r="L389" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="390" spans="1:11" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="390" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A390" s="2">
         <v>135533685</v>
       </c>
@@ -17819,10 +17815,10 @@
         <v>402</v>
       </c>
       <c r="L390" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="391" spans="1:11" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="391" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A391" s="2">
         <v>135534047</v>
       </c>
@@ -17857,10 +17853,10 @@
         <v>403</v>
       </c>
       <c r="L391" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="392" spans="1:11" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="392" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A392" s="2">
         <v>135534136</v>
       </c>
@@ -17895,10 +17891,10 @@
         <v>404</v>
       </c>
       <c r="L392" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="393" spans="1:11" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="393" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A393" s="2">
         <v>135534757</v>
       </c>
@@ -17933,10 +17929,10 @@
         <v>405</v>
       </c>
       <c r="L393" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="394" spans="1:11" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="394" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A394" s="2">
         <v>135534774</v>
       </c>
@@ -17971,10 +17967,10 @@
         <v>406</v>
       </c>
       <c r="L394" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="395" spans="1:11" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="395" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A395" s="2">
         <v>135534943</v>
       </c>
@@ -18009,10 +18005,10 @@
         <v>407</v>
       </c>
       <c r="L395" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="396" spans="1:11" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="396" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A396" s="2">
         <v>135535329</v>
       </c>
@@ -18047,10 +18043,10 @@
         <v>408</v>
       </c>
       <c r="L396" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="397" spans="1:11" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="397" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A397" s="2">
         <v>135535483</v>
       </c>
@@ -18085,10 +18081,10 @@
         <v>409</v>
       </c>
       <c r="L397" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="398" spans="1:11" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="398" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A398" s="2">
         <v>135535712</v>
       </c>
@@ -18123,10 +18119,10 @@
         <v>410</v>
       </c>
       <c r="L398" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="399" spans="1:11" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="399" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A399" s="2">
         <v>135536484</v>
       </c>
@@ -18161,10 +18157,10 @@
         <v>411</v>
       </c>
       <c r="L399" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="400" spans="1:11" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="400" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A400" s="2">
         <v>135536676</v>
       </c>
@@ -18199,10 +18195,10 @@
         <v>412</v>
       </c>
       <c r="L400" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="401" spans="1:11" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="401" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A401" s="2">
         <v>135537237</v>
       </c>
@@ -18237,10 +18233,10 @@
         <v>413</v>
       </c>
       <c r="L401" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="402" spans="1:11" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="402" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A402" s="2">
         <v>135537351</v>
       </c>
@@ -18275,10 +18271,10 @@
         <v>414</v>
       </c>
       <c r="L402" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="403" spans="1:11" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="403" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A403" s="2">
         <v>135537525</v>
       </c>
@@ -18313,10 +18309,10 @@
         <v>415</v>
       </c>
       <c r="L403" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="404" spans="1:11" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="404" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A404" s="2">
         <v>135537629</v>
       </c>
@@ -18351,10 +18347,10 @@
         <v>416</v>
       </c>
       <c r="L404" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="405" spans="1:11" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="405" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A405" s="2">
         <v>135538335</v>
       </c>
@@ -18389,10 +18385,10 @@
         <v>417</v>
       </c>
       <c r="L405" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="406" spans="1:11" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="406" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A406" s="2">
         <v>135538805</v>
       </c>
@@ -18427,10 +18423,10 @@
         <v>418</v>
       </c>
       <c r="L406" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="407" spans="1:11" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="407" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A407" s="2">
         <v>135539173</v>
       </c>
@@ -18465,10 +18461,10 @@
         <v>419</v>
       </c>
       <c r="L407" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="408" spans="1:11" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="408" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A408" s="2">
         <v>135539218</v>
       </c>
@@ -18503,10 +18499,10 @@
         <v>420</v>
       </c>
       <c r="L408" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="409" spans="1:11" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="409" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A409" s="2">
         <v>135539416</v>
       </c>
@@ -18541,10 +18537,10 @@
         <v>421</v>
       </c>
       <c r="L409" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="410" spans="1:11" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="410" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A410" s="2">
         <v>135539461</v>
       </c>
@@ -18579,10 +18575,10 @@
         <v>422</v>
       </c>
       <c r="L410" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="411" spans="1:11" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="411" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A411" s="2">
         <v>135539704</v>
       </c>
@@ -18617,10 +18613,10 @@
         <v>423</v>
       </c>
       <c r="L411" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="412" spans="1:11" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="412" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A412" s="2">
         <v>135539852</v>
       </c>
@@ -18655,10 +18651,10 @@
         <v>424</v>
       </c>
       <c r="L412" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="413" spans="1:11" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="413" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A413" s="2">
         <v>135539894</v>
       </c>
@@ -18693,10 +18689,10 @@
         <v>425</v>
       </c>
       <c r="L413" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="414" spans="1:11" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="414" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A414" s="2">
         <v>135540411</v>
       </c>
@@ -18731,10 +18727,10 @@
         <v>426</v>
       </c>
       <c r="L414" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="415" spans="1:11" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="415" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A415" s="2">
         <v>135540560</v>
       </c>
@@ -18769,10 +18765,10 @@
         <v>427</v>
       </c>
       <c r="L415" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="416" spans="1:11" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="416" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A416" s="2">
         <v>135540943</v>
       </c>
@@ -18807,10 +18803,10 @@
         <v>428</v>
       </c>
       <c r="L416" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="417" spans="1:11" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="417" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A417" s="2">
         <v>135540994</v>
       </c>
@@ -18845,10 +18841,10 @@
         <v>429</v>
       </c>
       <c r="L417" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="418" spans="1:11" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="418" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A418" s="2">
         <v>135540999</v>
       </c>
@@ -18883,10 +18879,10 @@
         <v>430</v>
       </c>
       <c r="L418" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="419" spans="1:11" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="419" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A419" s="2">
         <v>135541280</v>
       </c>
@@ -18921,10 +18917,10 @@
         <v>431</v>
       </c>
       <c r="L419" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="420" spans="1:11" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="420" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A420" s="2">
         <v>135541321</v>
       </c>
@@ -18959,10 +18955,10 @@
         <v>432</v>
       </c>
       <c r="L420" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="421" spans="1:11" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="421" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A421" s="2">
         <v>135541411</v>
       </c>
@@ -18997,10 +18993,10 @@
         <v>433</v>
       </c>
       <c r="L421" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="422" spans="1:11" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="422" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A422" s="2">
         <v>135541799</v>
       </c>
@@ -19035,10 +19031,10 @@
         <v>434</v>
       </c>
       <c r="L422" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="423" spans="1:11" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="423" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A423" s="2">
         <v>135541818</v>
       </c>
@@ -19073,10 +19069,10 @@
         <v>435</v>
       </c>
       <c r="L423" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="424" spans="1:11" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="424" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A424" s="2">
         <v>135543110</v>
       </c>
@@ -19111,10 +19107,10 @@
         <v>436</v>
       </c>
       <c r="L424" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="425" spans="1:11" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="425" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A425" s="2">
         <v>135543113</v>
       </c>
@@ -19149,10 +19145,10 @@
         <v>437</v>
       </c>
       <c r="L425" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="426" spans="1:11" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="426" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A426" s="2">
         <v>135543276</v>
       </c>
@@ -19187,10 +19183,10 @@
         <v>438</v>
       </c>
       <c r="L426" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="427" spans="1:11" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="427" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A427" s="2">
         <v>135543484</v>
       </c>
@@ -19225,10 +19221,10 @@
         <v>439</v>
       </c>
       <c r="L427" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="428" spans="1:11" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="428" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A428" s="2">
         <v>135543519</v>
       </c>
@@ -19263,10 +19259,10 @@
         <v>440</v>
       </c>
       <c r="L428" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="429" spans="1:11" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="429" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A429" s="2">
         <v>135543980</v>
       </c>
@@ -19301,10 +19297,10 @@
         <v>441</v>
       </c>
       <c r="L429" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="430" spans="1:11" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="430" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A430" s="2">
         <v>135544229</v>
       </c>
@@ -19339,10 +19335,10 @@
         <v>442</v>
       </c>
       <c r="L430" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="431" spans="1:11" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="431" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A431" s="2">
         <v>135544302</v>
       </c>
@@ -19377,10 +19373,10 @@
         <v>443</v>
       </c>
       <c r="L431" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="432" spans="1:11" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="432" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A432" s="2">
         <v>135544508</v>
       </c>
@@ -19415,10 +19411,10 @@
         <v>444</v>
       </c>
       <c r="L432" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="433" spans="1:11" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="433" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A433" s="2">
         <v>135544733</v>
       </c>
@@ -19453,10 +19449,10 @@
         <v>445</v>
       </c>
       <c r="L433" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="434" spans="1:11" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="434" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A434" s="2">
         <v>135544964</v>
       </c>
@@ -19491,10 +19487,10 @@
         <v>446</v>
       </c>
       <c r="L434" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="435" spans="1:11" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="435" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A435" s="2">
         <v>135545178</v>
       </c>
@@ -19529,10 +19525,10 @@
         <v>447</v>
       </c>
       <c r="L435" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="436" spans="1:11" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="436" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A436" s="2">
         <v>135545304</v>
       </c>
@@ -19567,10 +19563,10 @@
         <v>448</v>
       </c>
       <c r="L436" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="437" spans="1:11" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="437" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A437" s="2">
         <v>135545514</v>
       </c>
@@ -19605,10 +19601,10 @@
         <v>449</v>
       </c>
       <c r="L437" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="438" spans="1:11" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="438" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A438" s="2">
         <v>135545531</v>
       </c>
@@ -19643,10 +19639,10 @@
         <v>450</v>
       </c>
       <c r="L438" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="439" spans="1:11" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="439" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A439" s="2">
         <v>135546105</v>
       </c>
@@ -19681,10 +19677,10 @@
         <v>451</v>
       </c>
       <c r="L439" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="440" spans="1:11" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="440" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A440" s="2">
         <v>135546331</v>
       </c>
@@ -19719,10 +19715,10 @@
         <v>452</v>
       </c>
       <c r="L440" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="441" spans="1:11" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="441" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A441" s="2">
         <v>135546482</v>
       </c>
@@ -19757,10 +19753,10 @@
         <v>453</v>
       </c>
       <c r="L441" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="442" spans="1:11" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="442" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A442" s="2">
         <v>135546631</v>
       </c>
@@ -19795,10 +19791,10 @@
         <v>454</v>
       </c>
       <c r="L442" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="443" spans="1:11" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="443" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A443" s="2">
         <v>135546717</v>
       </c>
@@ -19833,10 +19829,10 @@
         <v>455</v>
       </c>
       <c r="L443" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="444" spans="1:11" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="444" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A444" s="2">
         <v>135547750</v>
       </c>
@@ -19871,10 +19867,10 @@
         <v>456</v>
       </c>
       <c r="L444" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="445" spans="1:11" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="445" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A445" s="2">
         <v>135547895</v>
       </c>
@@ -19909,10 +19905,10 @@
         <v>457</v>
       </c>
       <c r="L445" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="446" spans="1:11" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="446" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A446" s="2">
         <v>135548134</v>
       </c>
@@ -19947,10 +19943,10 @@
         <v>458</v>
       </c>
       <c r="L446" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="447" spans="1:11" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="447" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A447" s="2">
         <v>135548303</v>
       </c>
@@ -19985,10 +19981,10 @@
         <v>459</v>
       </c>
       <c r="L447" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="448" spans="1:11" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="448" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A448" s="2">
         <v>135398279</v>
       </c>
@@ -20023,10 +20019,10 @@
         <v>460</v>
       </c>
       <c r="L448" t="s">
-        <v>742</v>
-      </c>
-    </row>
-    <row r="449" spans="1:11" x14ac:dyDescent="0.25">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="449" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A449" s="2">
         <v>135398457</v>
       </c>
@@ -20061,10 +20057,10 @@
         <v>461</v>
       </c>
       <c r="L449" t="s">
-        <v>742</v>
-      </c>
-    </row>
-    <row r="450" spans="1:11" x14ac:dyDescent="0.25">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="450" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A450" s="2">
         <v>135399497</v>
       </c>
@@ -20099,10 +20095,10 @@
         <v>462</v>
       </c>
       <c r="L450" t="s">
-        <v>742</v>
-      </c>
-    </row>
-    <row r="451" spans="1:11" x14ac:dyDescent="0.25">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="451" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A451" s="2">
         <v>135401329</v>
       </c>
@@ -20137,10 +20133,10 @@
         <v>463</v>
       </c>
       <c r="L451" t="s">
-        <v>742</v>
-      </c>
-    </row>
-    <row r="452" spans="1:11" x14ac:dyDescent="0.25">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="452" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A452" s="2">
         <v>135407591</v>
       </c>
@@ -20175,10 +20171,10 @@
         <v>464</v>
       </c>
       <c r="L452" t="s">
-        <v>742</v>
-      </c>
-    </row>
-    <row r="453" spans="1:11" x14ac:dyDescent="0.25">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="453" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A453" s="2">
         <v>135410500</v>
       </c>
@@ -20213,10 +20209,10 @@
         <v>465</v>
       </c>
       <c r="L453" t="s">
-        <v>742</v>
-      </c>
-    </row>
-    <row r="454" spans="1:11" x14ac:dyDescent="0.25">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="454" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A454" s="2">
         <v>135376055</v>
       </c>
@@ -20251,10 +20247,10 @@
         <v>466</v>
       </c>
       <c r="L454" t="s">
-        <v>743</v>
-      </c>
-    </row>
-    <row r="455" spans="1:11" x14ac:dyDescent="0.25">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="455" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A455" s="2">
         <v>131885054</v>
       </c>
@@ -20289,10 +20285,10 @@
         <v>467</v>
       </c>
       <c r="L455" t="s">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="456" spans="1:11" x14ac:dyDescent="0.25">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="456" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A456" s="2">
         <v>135472076</v>
       </c>
@@ -20327,10 +20323,10 @@
         <v>468</v>
       </c>
       <c r="L456" t="s">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="457" spans="1:11" x14ac:dyDescent="0.25">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="457" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A457" s="2">
         <v>135513097</v>
       </c>
@@ -20365,10 +20361,10 @@
         <v>469</v>
       </c>
       <c r="L457" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="458" spans="1:11" x14ac:dyDescent="0.25">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="458" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A458" s="2">
         <v>132004619</v>
       </c>
@@ -20403,10 +20399,10 @@
         <v>470</v>
       </c>
       <c r="L458" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="459" spans="1:11" x14ac:dyDescent="0.25">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="459" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A459" s="2">
         <v>132584726</v>
       </c>
@@ -20441,10 +20437,10 @@
         <v>471</v>
       </c>
       <c r="L459" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="460" spans="1:11" x14ac:dyDescent="0.25">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="460" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A460" s="2">
         <v>133699733</v>
       </c>
@@ -20479,10 +20475,10 @@
         <v>472</v>
       </c>
       <c r="L460" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="461" spans="1:11" x14ac:dyDescent="0.25">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="461" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A461" s="2">
         <v>134348242</v>
       </c>
@@ -20517,10 +20513,10 @@
         <v>473</v>
       </c>
       <c r="L461" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="462" spans="1:11" x14ac:dyDescent="0.25">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="462" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A462" s="2">
         <v>134706206</v>
       </c>
@@ -20555,10 +20551,10 @@
         <v>474</v>
       </c>
       <c r="L462" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="463" spans="1:11" x14ac:dyDescent="0.25">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="463" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A463" s="2">
         <v>135531001</v>
       </c>
@@ -20593,10 +20589,10 @@
         <v>475</v>
       </c>
       <c r="L463" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="464" spans="1:11" x14ac:dyDescent="0.25">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="464" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A464" s="2">
         <v>135532483</v>
       </c>
@@ -20631,10 +20627,10 @@
         <v>476</v>
       </c>
       <c r="L464" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="465" spans="1:11" x14ac:dyDescent="0.25">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="465" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A465" s="2">
         <v>135533975</v>
       </c>
@@ -20669,10 +20665,10 @@
         <v>477</v>
       </c>
       <c r="L465" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="466" spans="1:11" x14ac:dyDescent="0.25">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="466" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A466" s="2">
         <v>135534609</v>
       </c>
@@ -20707,10 +20703,10 @@
         <v>478</v>
       </c>
       <c r="L466" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="467" spans="1:11" x14ac:dyDescent="0.25">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="467" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A467" s="2">
         <v>135534769</v>
       </c>
@@ -20745,10 +20741,10 @@
         <v>479</v>
       </c>
       <c r="L467" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="468" spans="1:11" x14ac:dyDescent="0.25">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="468" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A468" s="2">
         <v>135535821</v>
       </c>
@@ -20783,10 +20779,10 @@
         <v>480</v>
       </c>
       <c r="L468" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="469" spans="1:11" x14ac:dyDescent="0.25">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="469" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A469" s="2">
         <v>135537273</v>
       </c>
@@ -20821,10 +20817,10 @@
         <v>481</v>
       </c>
       <c r="L469" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="470" spans="1:11" x14ac:dyDescent="0.25">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="470" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A470" s="2">
         <v>135537449</v>
       </c>
@@ -20859,10 +20855,10 @@
         <v>482</v>
       </c>
       <c r="L470" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="471" spans="1:11" x14ac:dyDescent="0.25">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="471" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A471" s="2">
         <v>135537541</v>
       </c>
@@ -20897,10 +20893,10 @@
         <v>483</v>
       </c>
       <c r="L471" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="472" spans="1:11" x14ac:dyDescent="0.25">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="472" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A472" s="2">
         <v>135540015</v>
       </c>
@@ -20935,10 +20931,10 @@
         <v>484</v>
       </c>
       <c r="L472" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="473" spans="1:11" x14ac:dyDescent="0.25">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="473" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A473" s="2">
         <v>135540272</v>
       </c>
@@ -20973,10 +20969,10 @@
         <v>485</v>
       </c>
       <c r="L473" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="474" spans="1:11" x14ac:dyDescent="0.25">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="474" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A474" s="2">
         <v>135540951</v>
       </c>
@@ -21011,10 +21007,10 @@
         <v>486</v>
       </c>
       <c r="L474" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="475" spans="1:11" x14ac:dyDescent="0.25">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="475" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A475" s="2">
         <v>135544746</v>
       </c>
@@ -21049,10 +21045,10 @@
         <v>487</v>
       </c>
       <c r="L475" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="476" spans="1:11" x14ac:dyDescent="0.25">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="476" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A476" s="2">
         <v>135546301</v>
       </c>
@@ -21087,10 +21083,10 @@
         <v>488</v>
       </c>
       <c r="L476" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="477" spans="1:11" x14ac:dyDescent="0.25">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="477" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A477" s="2">
         <v>135547561</v>
       </c>
@@ -21125,10 +21121,10 @@
         <v>489</v>
       </c>
       <c r="L477" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="478" spans="1:11" x14ac:dyDescent="0.25">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="478" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A478" s="2">
         <v>135549569</v>
       </c>
@@ -21163,10 +21159,10 @@
         <v>490</v>
       </c>
       <c r="L478" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="479" spans="1:11" x14ac:dyDescent="0.25">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="479" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A479" s="2">
         <v>135515032</v>
       </c>
@@ -21201,10 +21197,10 @@
         <v>491</v>
       </c>
       <c r="L479" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="480" spans="1:11" x14ac:dyDescent="0.25">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="480" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A480" s="2">
         <v>135525110</v>
       </c>
@@ -21239,10 +21235,10 @@
         <v>492</v>
       </c>
       <c r="L480" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="481" spans="1:11" x14ac:dyDescent="0.25">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="481" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A481" s="2">
         <v>135528539</v>
       </c>
@@ -21277,10 +21273,10 @@
         <v>493</v>
       </c>
       <c r="L481" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="482" spans="1:11" x14ac:dyDescent="0.25">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="482" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A482" s="2">
         <v>135528576</v>
       </c>
@@ -21315,10 +21311,10 @@
         <v>494</v>
       </c>
       <c r="L482" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="483" spans="1:11" x14ac:dyDescent="0.25">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="483" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A483" s="2">
         <v>135529952</v>
       </c>
@@ -21353,10 +21349,10 @@
         <v>495</v>
       </c>
       <c r="L483" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="484" spans="1:11" x14ac:dyDescent="0.25">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="484" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A484" s="2">
         <v>135531037</v>
       </c>
@@ -21391,10 +21387,10 @@
         <v>496</v>
       </c>
       <c r="L484" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="485" spans="1:11" x14ac:dyDescent="0.25">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="485" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A485" s="2">
         <v>135531834</v>
       </c>
@@ -21429,10 +21425,10 @@
         <v>497</v>
       </c>
       <c r="L485" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="486" spans="1:11" x14ac:dyDescent="0.25">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="486" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A486" s="2">
         <v>135532460</v>
       </c>
@@ -21467,10 +21463,10 @@
         <v>498</v>
       </c>
       <c r="L486" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="487" spans="1:11" x14ac:dyDescent="0.25">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="487" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A487" s="2">
         <v>135533492</v>
       </c>
@@ -21505,10 +21501,10 @@
         <v>499</v>
       </c>
       <c r="L487" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="488" spans="1:11" x14ac:dyDescent="0.25">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="488" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A488" s="2">
         <v>135533994</v>
       </c>
@@ -21543,10 +21539,10 @@
         <v>500</v>
       </c>
       <c r="L488" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="489" spans="1:11" x14ac:dyDescent="0.25">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="489" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A489" s="2">
         <v>135534103</v>
       </c>
@@ -21581,10 +21577,10 @@
         <v>501</v>
       </c>
       <c r="L489" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="490" spans="1:11" x14ac:dyDescent="0.25">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="490" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A490" s="2">
         <v>135534145</v>
       </c>
@@ -21619,10 +21615,10 @@
         <v>502</v>
       </c>
       <c r="L490" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="491" spans="1:11" x14ac:dyDescent="0.25">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="491" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A491" s="2">
         <v>135535770</v>
       </c>
@@ -21657,10 +21653,10 @@
         <v>503</v>
       </c>
       <c r="L491" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="492" spans="1:11" x14ac:dyDescent="0.25">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="492" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A492" s="2">
         <v>135537516</v>
       </c>
@@ -21695,10 +21691,10 @@
         <v>504</v>
       </c>
       <c r="L492" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="493" spans="1:11" x14ac:dyDescent="0.25">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="493" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A493" s="2">
         <v>135539624</v>
       </c>
@@ -21733,10 +21729,10 @@
         <v>505</v>
       </c>
       <c r="L493" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="494" spans="1:11" x14ac:dyDescent="0.25">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="494" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A494" s="2">
         <v>135540964</v>
       </c>
@@ -21771,10 +21767,10 @@
         <v>506</v>
       </c>
       <c r="L494" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="495" spans="1:11" x14ac:dyDescent="0.25">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="495" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A495" s="2">
         <v>135541347</v>
       </c>
@@ -21809,10 +21805,10 @@
         <v>507</v>
       </c>
       <c r="L495" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="496" spans="1:11" x14ac:dyDescent="0.25">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="496" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A496" s="2">
         <v>135541719</v>
       </c>
@@ -21847,10 +21843,10 @@
         <v>508</v>
       </c>
       <c r="L496" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="497" spans="1:11" x14ac:dyDescent="0.25">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="497" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A497" s="2">
         <v>135542340</v>
       </c>
@@ -21885,10 +21881,10 @@
         <v>509</v>
       </c>
       <c r="L497" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="498" spans="1:11" x14ac:dyDescent="0.25">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="498" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A498" s="2">
         <v>135543352</v>
       </c>
@@ -21923,10 +21919,10 @@
         <v>510</v>
       </c>
       <c r="L498" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="499" spans="1:11" x14ac:dyDescent="0.25">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="499" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A499" s="2">
         <v>135543618</v>
       </c>
@@ -21961,10 +21957,10 @@
         <v>511</v>
       </c>
       <c r="L499" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="500" spans="1:11" x14ac:dyDescent="0.25">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="500" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A500" s="2">
         <v>135543783</v>
       </c>
@@ -21999,10 +21995,10 @@
         <v>512</v>
       </c>
       <c r="L500" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="501" spans="1:11" x14ac:dyDescent="0.25">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="501" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A501" s="2">
         <v>135545615</v>
       </c>
@@ -22037,10 +22033,10 @@
         <v>513</v>
       </c>
       <c r="L501" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="502" spans="1:11" x14ac:dyDescent="0.25">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="502" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A502" s="2">
         <v>135546375</v>
       </c>
@@ -22075,10 +22071,10 @@
         <v>514</v>
       </c>
       <c r="L502" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="503" spans="1:11" x14ac:dyDescent="0.25">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="503" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A503" s="2">
         <v>135547917</v>
       </c>
@@ -22113,10 +22109,10 @@
         <v>515</v>
       </c>
       <c r="L503" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="504" spans="1:11" x14ac:dyDescent="0.25">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="504" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A504" s="2">
         <v>135547978</v>
       </c>
@@ -22151,10 +22147,10 @@
         <v>516</v>
       </c>
       <c r="L504" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="505" spans="1:11" x14ac:dyDescent="0.25">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="505" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A505" s="2">
         <v>135548120</v>
       </c>
@@ -22189,10 +22185,10 @@
         <v>517</v>
       </c>
       <c r="L505" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="506" spans="1:11" x14ac:dyDescent="0.25">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="506" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A506" s="2">
         <v>135550557</v>
       </c>
@@ -22227,10 +22223,10 @@
         <v>518</v>
       </c>
       <c r="L506" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="507" spans="1:11" x14ac:dyDescent="0.25">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="507" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A507" s="2">
         <v>134903909</v>
       </c>
@@ -22264,11 +22260,9 @@
       <c r="K507" s="3" t="s">
         <v>519</v>
       </c>
-      <c r="L507" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="508" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L507"/>
+    </row>
+    <row r="508" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A508" s="2">
         <v>135395708</v>
       </c>
@@ -22302,11 +22296,9 @@
       <c r="K508" s="3" t="s">
         <v>520</v>
       </c>
-      <c r="L508" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="509" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L508"/>
+    </row>
+    <row r="509" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A509" s="2">
         <v>135399752</v>
       </c>
@@ -22340,11 +22332,9 @@
       <c r="K509" s="3" t="s">
         <v>521</v>
       </c>
-      <c r="L509" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="510" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L509"/>
+    </row>
+    <row r="510" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A510" s="2">
         <v>135408852</v>
       </c>
@@ -22378,11 +22368,9 @@
       <c r="K510" s="3" t="s">
         <v>522</v>
       </c>
-      <c r="L510" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="511" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L510"/>
+    </row>
+    <row r="511" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A511" s="2">
         <v>135422265</v>
       </c>
@@ -22416,11 +22404,9 @@
       <c r="K511" s="3" t="s">
         <v>523</v>
       </c>
-      <c r="L511" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="512" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L511"/>
+    </row>
+    <row r="512" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A512" s="2">
         <v>135440521</v>
       </c>
@@ -22454,11 +22440,9 @@
       <c r="K512" s="3" t="s">
         <v>524</v>
       </c>
-      <c r="L512" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="513" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L512"/>
+    </row>
+    <row r="513" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A513" s="2">
         <v>135447663</v>
       </c>
@@ -22492,11 +22476,9 @@
       <c r="K513" s="3" t="s">
         <v>525</v>
       </c>
-      <c r="L513" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="514" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L513"/>
+    </row>
+    <row r="514" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A514" s="2">
         <v>135465880</v>
       </c>
@@ -22530,11 +22512,9 @@
       <c r="K514" s="3" t="s">
         <v>526</v>
       </c>
-      <c r="L514" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="515" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L514"/>
+    </row>
+    <row r="515" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A515" s="2">
         <v>135477838</v>
       </c>
@@ -22568,11 +22548,9 @@
       <c r="K515" s="3" t="s">
         <v>527</v>
       </c>
-      <c r="L515" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="516" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L515"/>
+    </row>
+    <row r="516" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A516" s="2">
         <v>135492855</v>
       </c>
@@ -22606,11 +22584,9 @@
       <c r="K516" s="3" t="s">
         <v>528</v>
       </c>
-      <c r="L516" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="517" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L516"/>
+    </row>
+    <row r="517" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A517" s="2">
         <v>135505915</v>
       </c>
@@ -22644,11 +22620,9 @@
       <c r="K517" s="3" t="s">
         <v>529</v>
       </c>
-      <c r="L517" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="518" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L517"/>
+    </row>
+    <row r="518" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A518" s="2">
         <v>135512426</v>
       </c>
@@ -22682,11 +22656,9 @@
       <c r="K518" s="3" t="s">
         <v>530</v>
       </c>
-      <c r="L518" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="519" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L518"/>
+    </row>
+    <row r="519" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A519" s="2">
         <v>135514142</v>
       </c>
@@ -22720,11 +22692,9 @@
       <c r="K519" s="3" t="s">
         <v>531</v>
       </c>
-      <c r="L519" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="520" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L519"/>
+    </row>
+    <row r="520" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A520" s="2">
         <v>135515374</v>
       </c>
@@ -22758,11 +22728,9 @@
       <c r="K520" s="3" t="s">
         <v>532</v>
       </c>
-      <c r="L520" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="521" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L520"/>
+    </row>
+    <row r="521" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A521" s="2">
         <v>135525758</v>
       </c>
@@ -22796,11 +22764,9 @@
       <c r="K521" s="3" t="s">
         <v>533</v>
       </c>
-      <c r="L521" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="522" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L521"/>
+    </row>
+    <row r="522" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A522" s="2">
         <v>135526544</v>
       </c>
@@ -22834,11 +22800,9 @@
       <c r="K522" s="3" t="s">
         <v>534</v>
       </c>
-      <c r="L522" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="523" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L522"/>
+    </row>
+    <row r="523" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A523" s="2">
         <v>135531149</v>
       </c>
@@ -22872,11 +22836,9 @@
       <c r="K523" s="3" t="s">
         <v>535</v>
       </c>
-      <c r="L523" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="524" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L523"/>
+    </row>
+    <row r="524" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A524" s="2">
         <v>135531544</v>
       </c>
@@ -22910,11 +22872,9 @@
       <c r="K524" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="L524" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="525" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L524"/>
+    </row>
+    <row r="525" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A525" s="2">
         <v>135534730</v>
       </c>
@@ -22948,11 +22908,9 @@
       <c r="K525" s="3" t="s">
         <v>537</v>
       </c>
-      <c r="L525" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="526" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L525"/>
+    </row>
+    <row r="526" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A526" s="2">
         <v>135536610</v>
       </c>
@@ -22986,11 +22944,9 @@
       <c r="K526" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="L526" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="527" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L526"/>
+    </row>
+    <row r="527" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A527" s="2">
         <v>135540530</v>
       </c>
@@ -23024,11 +22980,9 @@
       <c r="K527" s="3" t="s">
         <v>539</v>
       </c>
-      <c r="L527" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="528" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L527"/>
+    </row>
+    <row r="528" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A528" s="2">
         <v>135544168</v>
       </c>
@@ -23062,11 +23016,9 @@
       <c r="K528" s="3" t="s">
         <v>540</v>
       </c>
-      <c r="L528" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="529" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L528"/>
+    </row>
+    <row r="529" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A529" s="2">
         <v>135546306</v>
       </c>
@@ -23100,11 +23052,9 @@
       <c r="K529" s="3" t="s">
         <v>541</v>
       </c>
-      <c r="L529" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="530" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L529"/>
+    </row>
+    <row r="530" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A530" s="2">
         <v>135546856</v>
       </c>
@@ -23138,11 +23088,9 @@
       <c r="K530" s="3" t="s">
         <v>542</v>
       </c>
-      <c r="L530" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="531" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L530"/>
+    </row>
+    <row r="531" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A531" s="2">
         <v>134461774</v>
       </c>
@@ -23176,11 +23124,9 @@
       <c r="K531" s="3" t="s">
         <v>543</v>
       </c>
-      <c r="L531" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="532" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L531"/>
+    </row>
+    <row r="532" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A532" s="2">
         <v>135397940</v>
       </c>
@@ -23214,11 +23160,9 @@
       <c r="K532" s="3" t="s">
         <v>544</v>
       </c>
-      <c r="L532" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="533" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L532"/>
+    </row>
+    <row r="533" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A533" s="2">
         <v>135398323</v>
       </c>
@@ -23252,11 +23196,9 @@
       <c r="K533" s="3" t="s">
         <v>545</v>
       </c>
-      <c r="L533" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="534" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L533"/>
+    </row>
+    <row r="534" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A534" s="2">
         <v>135403149</v>
       </c>
@@ -23290,11 +23232,9 @@
       <c r="K534" s="3" t="s">
         <v>546</v>
       </c>
-      <c r="L534" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="535" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L534"/>
+    </row>
+    <row r="535" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A535" s="2">
         <v>135403812</v>
       </c>
@@ -23328,11 +23268,9 @@
       <c r="K535" s="3" t="s">
         <v>547</v>
       </c>
-      <c r="L535" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="536" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L535"/>
+    </row>
+    <row r="536" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A536" s="2">
         <v>135405847</v>
       </c>
@@ -23366,11 +23304,9 @@
       <c r="K536" s="3" t="s">
         <v>548</v>
       </c>
-      <c r="L536" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="537" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L536"/>
+    </row>
+    <row r="537" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A537" s="2">
         <v>135410906</v>
       </c>
@@ -23404,11 +23340,9 @@
       <c r="K537" s="3" t="s">
         <v>549</v>
       </c>
-      <c r="L537" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="538" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L537"/>
+    </row>
+    <row r="538" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A538" s="2">
         <v>135412680</v>
       </c>
@@ -23442,11 +23376,9 @@
       <c r="K538" s="3" t="s">
         <v>550</v>
       </c>
-      <c r="L538" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="539" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L538"/>
+    </row>
+    <row r="539" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A539" s="2">
         <v>135413971</v>
       </c>
@@ -23480,11 +23412,9 @@
       <c r="K539" s="3" t="s">
         <v>551</v>
       </c>
-      <c r="L539" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="540" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L539"/>
+    </row>
+    <row r="540" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A540" s="2">
         <v>135355956</v>
       </c>
@@ -23518,11 +23448,9 @@
       <c r="K540" s="3" t="s">
         <v>552</v>
       </c>
-      <c r="L540" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="541" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L540"/>
+    </row>
+    <row r="541" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A541" s="2">
         <v>135412259</v>
       </c>
@@ -23556,11 +23484,9 @@
       <c r="K541" s="3" t="s">
         <v>553</v>
       </c>
-      <c r="L541" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="542" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L541"/>
+    </row>
+    <row r="542" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A542" s="2">
         <v>135444532</v>
       </c>
@@ -23594,11 +23520,9 @@
       <c r="K542" s="3" t="s">
         <v>554</v>
       </c>
-      <c r="L542" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="543" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L542"/>
+    </row>
+    <row r="543" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A543" s="2">
         <v>135449304</v>
       </c>
@@ -23632,11 +23556,9 @@
       <c r="K543" s="3" t="s">
         <v>555</v>
       </c>
-      <c r="L543" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="544" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L543"/>
+    </row>
+    <row r="544" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A544" s="2">
         <v>135449664</v>
       </c>
@@ -23670,11 +23592,9 @@
       <c r="K544" s="3" t="s">
         <v>556</v>
       </c>
-      <c r="L544" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="545" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L544"/>
+    </row>
+    <row r="545" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A545" s="2">
         <v>135453927</v>
       </c>
@@ -23708,11 +23628,9 @@
       <c r="K545" s="3" t="s">
         <v>557</v>
       </c>
-      <c r="L545" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="546" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L545"/>
+    </row>
+    <row r="546" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A546" s="2">
         <v>135458813</v>
       </c>
@@ -23746,11 +23664,9 @@
       <c r="K546" s="3" t="s">
         <v>558</v>
       </c>
-      <c r="L546" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="547" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L546"/>
+    </row>
+    <row r="547" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A547" s="2">
         <v>135463444</v>
       </c>
@@ -23784,11 +23700,9 @@
       <c r="K547" s="3" t="s">
         <v>559</v>
       </c>
-      <c r="L547" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="548" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L547"/>
+    </row>
+    <row r="548" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A548" s="2">
         <v>135468302</v>
       </c>
@@ -23822,11 +23736,9 @@
       <c r="K548" s="3" t="s">
         <v>560</v>
       </c>
-      <c r="L548" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="549" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L548"/>
+    </row>
+    <row r="549" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A549" s="2">
         <v>135468369</v>
       </c>
@@ -23860,11 +23772,9 @@
       <c r="K549" s="3" t="s">
         <v>561</v>
       </c>
-      <c r="L549" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="550" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L549"/>
+    </row>
+    <row r="550" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A550" s="2">
         <v>135468882</v>
       </c>
@@ -23898,11 +23808,9 @@
       <c r="K550" s="3" t="s">
         <v>562</v>
       </c>
-      <c r="L550" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="551" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L550"/>
+    </row>
+    <row r="551" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A551" s="2">
         <v>135468999</v>
       </c>
@@ -23936,11 +23844,9 @@
       <c r="K551" s="3" t="s">
         <v>563</v>
       </c>
-      <c r="L551" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="552" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L551"/>
+    </row>
+    <row r="552" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A552" s="2">
         <v>135477898</v>
       </c>
@@ -23974,11 +23880,9 @@
       <c r="K552" s="3" t="s">
         <v>564</v>
       </c>
-      <c r="L552" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="553" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L552"/>
+    </row>
+    <row r="553" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A553" s="2">
         <v>135498470</v>
       </c>
@@ -24012,11 +23916,9 @@
       <c r="K553" s="3" t="s">
         <v>565</v>
       </c>
-      <c r="L553" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="554" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L553"/>
+    </row>
+    <row r="554" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A554" s="2">
         <v>135396203</v>
       </c>
@@ -24050,11 +23952,9 @@
       <c r="K554" s="3" t="s">
         <v>566</v>
       </c>
-      <c r="L554" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="555" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L554"/>
+    </row>
+    <row r="555" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A555" s="2">
         <v>135397516</v>
       </c>
@@ -24088,11 +23988,9 @@
       <c r="K555" s="3" t="s">
         <v>567</v>
       </c>
-      <c r="L555" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="556" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L555"/>
+    </row>
+    <row r="556" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A556" s="2">
         <v>135407424</v>
       </c>
@@ -24126,11 +24024,9 @@
       <c r="K556" s="3" t="s">
         <v>568</v>
       </c>
-      <c r="L556" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="557" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L556"/>
+    </row>
+    <row r="557" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A557" s="2">
         <v>135410154</v>
       </c>
@@ -24164,11 +24060,9 @@
       <c r="K557" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="L557" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="558" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L557"/>
+    </row>
+    <row r="558" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A558" s="2">
         <v>135410611</v>
       </c>
@@ -24202,11 +24096,9 @@
       <c r="K558" s="3" t="s">
         <v>570</v>
       </c>
-      <c r="L558" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="559" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L558"/>
+    </row>
+    <row r="559" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A559" s="2">
         <v>135410989</v>
       </c>
@@ -24240,11 +24132,9 @@
       <c r="K559" s="3" t="s">
         <v>571</v>
       </c>
-      <c r="L559" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="560" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L559"/>
+    </row>
+    <row r="560" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A560" s="2">
         <v>132536898</v>
       </c>
@@ -24278,11 +24168,9 @@
       <c r="K560" s="3" t="s">
         <v>572</v>
       </c>
-      <c r="L560" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="561" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L560"/>
+    </row>
+    <row r="561" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A561" s="2">
         <v>135531307</v>
       </c>
@@ -24316,11 +24204,9 @@
       <c r="K561" s="3" t="s">
         <v>573</v>
       </c>
-      <c r="L561" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="562" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L561"/>
+    </row>
+    <row r="562" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A562" s="2">
         <v>135531930</v>
       </c>
@@ -24354,11 +24240,9 @@
       <c r="K562" s="3" t="s">
         <v>574</v>
       </c>
-      <c r="L562" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="563" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L562"/>
+    </row>
+    <row r="563" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A563" s="2">
         <v>135532326</v>
       </c>
@@ -24392,11 +24276,9 @@
       <c r="K563" s="3" t="s">
         <v>575</v>
       </c>
-      <c r="L563" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="564" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L563"/>
+    </row>
+    <row r="564" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A564" s="2">
         <v>135535811</v>
       </c>
@@ -24430,11 +24312,9 @@
       <c r="K564" s="3" t="s">
         <v>576</v>
       </c>
-      <c r="L564" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="565" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L564"/>
+    </row>
+    <row r="565" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A565" s="2">
         <v>135539745</v>
       </c>
@@ -24468,11 +24348,9 @@
       <c r="K565" s="3" t="s">
         <v>577</v>
       </c>
-      <c r="L565" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="566" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L565"/>
+    </row>
+    <row r="566" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A566" s="2">
         <v>135540855</v>
       </c>
@@ -24506,11 +24384,9 @@
       <c r="K566" s="3" t="s">
         <v>578</v>
       </c>
-      <c r="L566" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="567" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L566"/>
+    </row>
+    <row r="567" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A567" s="2">
         <v>135540930</v>
       </c>
@@ -24544,11 +24420,9 @@
       <c r="K567" s="3" t="s">
         <v>579</v>
       </c>
-      <c r="L567" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="568" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L567"/>
+    </row>
+    <row r="568" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A568" s="2">
         <v>135543375</v>
       </c>
@@ -24582,11 +24456,9 @@
       <c r="K568" s="3" t="s">
         <v>580</v>
       </c>
-      <c r="L568" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="569" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L568"/>
+    </row>
+    <row r="569" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A569" s="2">
         <v>135544065</v>
       </c>
@@ -24620,11 +24492,9 @@
       <c r="K569" s="3" t="s">
         <v>581</v>
       </c>
-      <c r="L569" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="570" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L569"/>
+    </row>
+    <row r="570" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A570" s="2">
         <v>135545222</v>
       </c>
@@ -24658,11 +24528,9 @@
       <c r="K570" s="3" t="s">
         <v>582</v>
       </c>
-      <c r="L570" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="571" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L570"/>
+    </row>
+    <row r="571" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A571" s="2">
         <v>135545551</v>
       </c>
@@ -24696,11 +24564,9 @@
       <c r="K571" s="3" t="s">
         <v>583</v>
       </c>
-      <c r="L571" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="572" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L571"/>
+    </row>
+    <row r="572" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A572" s="2">
         <v>135547342</v>
       </c>
@@ -24734,11 +24600,9 @@
       <c r="K572" s="3" t="s">
         <v>584</v>
       </c>
-      <c r="L572" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="573" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L572"/>
+    </row>
+    <row r="573" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A573" s="2">
         <v>135356500</v>
       </c>
@@ -24772,11 +24636,9 @@
       <c r="K573" s="3" t="s">
         <v>585</v>
       </c>
-      <c r="L573" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="574" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L573"/>
+    </row>
+    <row r="574" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A574" s="2">
         <v>135377794</v>
       </c>
@@ -24810,11 +24672,9 @@
       <c r="K574" s="3" t="s">
         <v>586</v>
       </c>
-      <c r="L574" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="575" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L574"/>
+    </row>
+    <row r="575" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A575" s="2">
         <v>135380046</v>
       </c>
@@ -24848,11 +24708,9 @@
       <c r="K575" s="3" t="s">
         <v>587</v>
       </c>
-      <c r="L575" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="576" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L575"/>
+    </row>
+    <row r="576" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A576" s="2">
         <v>135418972</v>
       </c>
@@ -24886,11 +24744,9 @@
       <c r="K576" s="3" t="s">
         <v>588</v>
       </c>
-      <c r="L576" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="577" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L576"/>
+    </row>
+    <row r="577" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A577" s="2">
         <v>135429481</v>
       </c>
@@ -24924,11 +24780,9 @@
       <c r="K577" s="3" t="s">
         <v>589</v>
       </c>
-      <c r="L577" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="578" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L577"/>
+    </row>
+    <row r="578" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A578" s="2">
         <v>135432748</v>
       </c>
@@ -24962,11 +24816,9 @@
       <c r="K578" s="3" t="s">
         <v>590</v>
       </c>
-      <c r="L578" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="579" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L578"/>
+    </row>
+    <row r="579" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A579" s="2">
         <v>135444690</v>
       </c>
@@ -25000,11 +24852,9 @@
       <c r="K579" s="3" t="s">
         <v>591</v>
       </c>
-      <c r="L579" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="580" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L579"/>
+    </row>
+    <row r="580" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A580" s="2">
         <v>135446863</v>
       </c>
@@ -25038,11 +24888,9 @@
       <c r="K580" s="3" t="s">
         <v>592</v>
       </c>
-      <c r="L580" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="581" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L580"/>
+    </row>
+    <row r="581" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A581" s="2">
         <v>135446867</v>
       </c>
@@ -25076,11 +24924,9 @@
       <c r="K581" s="3" t="s">
         <v>593</v>
       </c>
-      <c r="L581" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="582" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L581"/>
+    </row>
+    <row r="582" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A582" s="2">
         <v>135450787</v>
       </c>
@@ -25114,11 +24960,9 @@
       <c r="K582" s="3" t="s">
         <v>594</v>
       </c>
-      <c r="L582" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="583" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L582"/>
+    </row>
+    <row r="583" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A583" s="2">
         <v>135453985</v>
       </c>
@@ -25152,11 +24996,9 @@
       <c r="K583" s="3" t="s">
         <v>595</v>
       </c>
-      <c r="L583" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="584" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L583"/>
+    </row>
+    <row r="584" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A584" s="2">
         <v>135454453</v>
       </c>
@@ -25190,11 +25032,9 @@
       <c r="K584" s="3" t="s">
         <v>596</v>
       </c>
-      <c r="L584" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="585" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L584"/>
+    </row>
+    <row r="585" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A585" s="2">
         <v>135461082</v>
       </c>
@@ -25228,11 +25068,9 @@
       <c r="K585" s="3" t="s">
         <v>597</v>
       </c>
-      <c r="L585" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="586" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L585"/>
+    </row>
+    <row r="586" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A586" s="2">
         <v>135467563</v>
       </c>
@@ -25266,11 +25104,9 @@
       <c r="K586" s="3" t="s">
         <v>598</v>
       </c>
-      <c r="L586" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="587" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L586"/>
+    </row>
+    <row r="587" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A587" s="2">
         <v>135468044</v>
       </c>
@@ -25304,11 +25140,9 @@
       <c r="K587" s="3" t="s">
         <v>599</v>
       </c>
-      <c r="L587" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="588" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L587"/>
+    </row>
+    <row r="588" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A588" s="2">
         <v>135471642</v>
       </c>
@@ -25342,11 +25176,9 @@
       <c r="K588" s="3" t="s">
         <v>600</v>
       </c>
-      <c r="L588" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="589" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L588"/>
+    </row>
+    <row r="589" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A589" s="2">
         <v>135474963</v>
       </c>
@@ -25380,11 +25212,9 @@
       <c r="K589" s="3" t="s">
         <v>601</v>
       </c>
-      <c r="L589" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="590" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L589"/>
+    </row>
+    <row r="590" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A590" s="2">
         <v>135475042</v>
       </c>
@@ -25418,11 +25248,9 @@
       <c r="K590" s="3" t="s">
         <v>602</v>
       </c>
-      <c r="L590" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="591" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L590"/>
+    </row>
+    <row r="591" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A591" s="2">
         <v>135484397</v>
       </c>
@@ -25456,11 +25284,9 @@
       <c r="K591" s="3" t="s">
         <v>603</v>
       </c>
-      <c r="L591" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="592" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L591"/>
+    </row>
+    <row r="592" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A592" s="2">
         <v>135488735</v>
       </c>
@@ -25494,11 +25320,9 @@
       <c r="K592" s="3" t="s">
         <v>604</v>
       </c>
-      <c r="L592" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="593" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L592"/>
+    </row>
+    <row r="593" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A593" s="2">
         <v>135488842</v>
       </c>
@@ -25532,11 +25356,9 @@
       <c r="K593" s="3" t="s">
         <v>605</v>
       </c>
-      <c r="L593" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="594" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L593"/>
+    </row>
+    <row r="594" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A594" s="2">
         <v>135488953</v>
       </c>
@@ -25570,11 +25392,9 @@
       <c r="K594" s="3" t="s">
         <v>606</v>
       </c>
-      <c r="L594" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="595" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L594"/>
+    </row>
+    <row r="595" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A595" s="2">
         <v>135489285</v>
       </c>
@@ -25608,11 +25428,9 @@
       <c r="K595" s="3" t="s">
         <v>607</v>
       </c>
-      <c r="L595" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="596" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L595"/>
+    </row>
+    <row r="596" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A596" s="2">
         <v>135491436</v>
       </c>
@@ -25646,11 +25464,9 @@
       <c r="K596" s="3" t="s">
         <v>608</v>
       </c>
-      <c r="L596" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="597" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L596"/>
+    </row>
+    <row r="597" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A597" s="2">
         <v>135491751</v>
       </c>
@@ -25684,11 +25500,9 @@
       <c r="K597" s="3" t="s">
         <v>609</v>
       </c>
-      <c r="L597" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="598" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L597"/>
+    </row>
+    <row r="598" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A598" s="2">
         <v>135492039</v>
       </c>
@@ -25722,11 +25536,9 @@
       <c r="K598" s="3" t="s">
         <v>610</v>
       </c>
-      <c r="L598" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="599" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L598"/>
+    </row>
+    <row r="599" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A599" s="2">
         <v>135494206</v>
       </c>
@@ -25760,11 +25572,9 @@
       <c r="K599" s="3" t="s">
         <v>611</v>
       </c>
-      <c r="L599" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="600" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L599"/>
+    </row>
+    <row r="600" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A600" s="2">
         <v>135498142</v>
       </c>
@@ -25798,11 +25608,9 @@
       <c r="K600" s="3" t="s">
         <v>612</v>
       </c>
-      <c r="L600" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="601" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L600"/>
+    </row>
+    <row r="601" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A601" s="2">
         <v>135499140</v>
       </c>
@@ -25836,11 +25644,9 @@
       <c r="K601" s="3" t="s">
         <v>613</v>
       </c>
-      <c r="L601" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="602" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L601"/>
+    </row>
+    <row r="602" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A602" s="2">
         <v>135499501</v>
       </c>
@@ -25874,11 +25680,9 @@
       <c r="K602" s="3" t="s">
         <v>614</v>
       </c>
-      <c r="L602" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="603" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L602"/>
+    </row>
+    <row r="603" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A603" s="2">
         <v>135499807</v>
       </c>
@@ -25912,11 +25716,9 @@
       <c r="K603" s="3" t="s">
         <v>615</v>
       </c>
-      <c r="L603" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="604" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L603"/>
+    </row>
+    <row r="604" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A604" s="2">
         <v>135503515</v>
       </c>
@@ -25950,11 +25752,9 @@
       <c r="K604" s="3" t="s">
         <v>616</v>
       </c>
-      <c r="L604" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="605" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L604"/>
+    </row>
+    <row r="605" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A605" s="2">
         <v>135503882</v>
       </c>
@@ -25988,11 +25788,9 @@
       <c r="K605" s="3" t="s">
         <v>617</v>
       </c>
-      <c r="L605" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="606" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L605"/>
+    </row>
+    <row r="606" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A606" s="2">
         <v>135504037</v>
       </c>
@@ -26026,11 +25824,9 @@
       <c r="K606" s="3" t="s">
         <v>618</v>
       </c>
-      <c r="L606" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="607" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L606"/>
+    </row>
+    <row r="607" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A607" s="2">
         <v>135507348</v>
       </c>
@@ -26064,11 +25860,9 @@
       <c r="K607" s="3" t="s">
         <v>619</v>
       </c>
-      <c r="L607" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="608" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L607"/>
+    </row>
+    <row r="608" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A608" s="2">
         <v>135507882</v>
       </c>
@@ -26102,11 +25896,9 @@
       <c r="K608" s="3" t="s">
         <v>620</v>
       </c>
-      <c r="L608" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="609" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L608"/>
+    </row>
+    <row r="609" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A609" s="2">
         <v>135508396</v>
       </c>
@@ -26140,11 +25932,9 @@
       <c r="K609" s="3" t="s">
         <v>621</v>
       </c>
-      <c r="L609" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="610" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L609"/>
+    </row>
+    <row r="610" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A610" s="2">
         <v>135508745</v>
       </c>
@@ -26178,11 +25968,9 @@
       <c r="K610" s="3" t="s">
         <v>622</v>
       </c>
-      <c r="L610" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="611" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L610"/>
+    </row>
+    <row r="611" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A611" s="2">
         <v>135509223</v>
       </c>
@@ -26216,11 +26004,9 @@
       <c r="K611" s="3" t="s">
         <v>623</v>
       </c>
-      <c r="L611" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="612" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L611"/>
+    </row>
+    <row r="612" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A612" s="2">
         <v>135510084</v>
       </c>
@@ -26254,11 +26040,9 @@
       <c r="K612" s="3" t="s">
         <v>624</v>
       </c>
-      <c r="L612" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="613" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L612"/>
+    </row>
+    <row r="613" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A613" s="2">
         <v>135510544</v>
       </c>
@@ -26292,11 +26076,9 @@
       <c r="K613" s="3" t="s">
         <v>625</v>
       </c>
-      <c r="L613" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="614" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L613"/>
+    </row>
+    <row r="614" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A614" s="2">
         <v>135510893</v>
       </c>
@@ -26330,11 +26112,9 @@
       <c r="K614" s="3" t="s">
         <v>626</v>
       </c>
-      <c r="L614" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="615" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L614"/>
+    </row>
+    <row r="615" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A615" s="2">
         <v>135511072</v>
       </c>
@@ -26368,11 +26148,9 @@
       <c r="K615" s="3" t="s">
         <v>627</v>
       </c>
-      <c r="L615" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="616" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L615"/>
+    </row>
+    <row r="616" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A616" s="2">
         <v>135511550</v>
       </c>
@@ -26406,11 +26184,9 @@
       <c r="K616" s="3" t="s">
         <v>628</v>
       </c>
-      <c r="L616" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="617" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L616"/>
+    </row>
+    <row r="617" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A617" s="2">
         <v>135511796</v>
       </c>
@@ -26444,11 +26220,9 @@
       <c r="K617" s="3" t="s">
         <v>629</v>
       </c>
-      <c r="L617" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="618" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L617"/>
+    </row>
+    <row r="618" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A618" s="2">
         <v>135512290</v>
       </c>
@@ -26482,11 +26256,9 @@
       <c r="K618" s="3" t="s">
         <v>630</v>
       </c>
-      <c r="L618" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="619" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L618"/>
+    </row>
+    <row r="619" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A619" s="2">
         <v>135513211</v>
       </c>
@@ -26520,11 +26292,9 @@
       <c r="K619" s="3" t="s">
         <v>631</v>
       </c>
-      <c r="L619" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="620" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L619"/>
+    </row>
+    <row r="620" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A620" s="2">
         <v>135513391</v>
       </c>
@@ -26558,11 +26328,9 @@
       <c r="K620" s="3" t="s">
         <v>632</v>
       </c>
-      <c r="L620" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="621" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L620"/>
+    </row>
+    <row r="621" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A621" s="2">
         <v>135513445</v>
       </c>
@@ -26596,11 +26364,9 @@
       <c r="K621" s="3" t="s">
         <v>633</v>
       </c>
-      <c r="L621" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="622" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L621"/>
+    </row>
+    <row r="622" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A622" s="2">
         <v>135513447</v>
       </c>
@@ -26634,11 +26400,9 @@
       <c r="K622" s="3" t="s">
         <v>634</v>
       </c>
-      <c r="L622" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="623" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L622"/>
+    </row>
+    <row r="623" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A623" s="2">
         <v>135513477</v>
       </c>
@@ -26672,11 +26436,9 @@
       <c r="K623" s="3" t="s">
         <v>635</v>
       </c>
-      <c r="L623" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="624" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L623"/>
+    </row>
+    <row r="624" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A624" s="2">
         <v>135513515</v>
       </c>
@@ -26710,11 +26472,9 @@
       <c r="K624" s="3" t="s">
         <v>636</v>
       </c>
-      <c r="L624" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="625" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L624"/>
+    </row>
+    <row r="625" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A625" s="2">
         <v>135513564</v>
       </c>
@@ -26748,11 +26508,9 @@
       <c r="K625" s="3" t="s">
         <v>637</v>
       </c>
-      <c r="L625" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="626" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L625"/>
+    </row>
+    <row r="626" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A626" s="2">
         <v>135514119</v>
       </c>
@@ -26786,11 +26544,9 @@
       <c r="K626" s="3" t="s">
         <v>638</v>
       </c>
-      <c r="L626" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="627" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L626"/>
+    </row>
+    <row r="627" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A627" s="2">
         <v>135514515</v>
       </c>
@@ -26824,11 +26580,9 @@
       <c r="K627" s="3" t="s">
         <v>639</v>
       </c>
-      <c r="L627" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="628" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L627"/>
+    </row>
+    <row r="628" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A628" s="2">
         <v>135514653</v>
       </c>
@@ -26862,11 +26616,9 @@
       <c r="K628" s="3" t="s">
         <v>640</v>
       </c>
-      <c r="L628" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="629" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L628"/>
+    </row>
+    <row r="629" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A629" s="2">
         <v>135515023</v>
       </c>
@@ -26900,11 +26652,9 @@
       <c r="K629" s="3" t="s">
         <v>641</v>
       </c>
-      <c r="L629" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="630" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L629"/>
+    </row>
+    <row r="630" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A630" s="2">
         <v>135515058</v>
       </c>
@@ -26938,11 +26688,9 @@
       <c r="K630" s="3" t="s">
         <v>642</v>
       </c>
-      <c r="L630" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="631" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L630"/>
+    </row>
+    <row r="631" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A631" s="2">
         <v>135515083</v>
       </c>
@@ -26976,11 +26724,9 @@
       <c r="K631" s="3" t="s">
         <v>643</v>
       </c>
-      <c r="L631" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="632" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L631"/>
+    </row>
+    <row r="632" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A632" s="2">
         <v>135515305</v>
       </c>
@@ -27014,11 +26760,9 @@
       <c r="K632" s="3" t="s">
         <v>644</v>
       </c>
-      <c r="L632" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="633" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L632"/>
+    </row>
+    <row r="633" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A633" s="2">
         <v>135515479</v>
       </c>
@@ -27052,11 +26796,9 @@
       <c r="K633" s="3" t="s">
         <v>645</v>
       </c>
-      <c r="L633" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="634" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L633"/>
+    </row>
+    <row r="634" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A634" s="2">
         <v>135515499</v>
       </c>
@@ -27090,11 +26832,9 @@
       <c r="K634" s="3" t="s">
         <v>646</v>
       </c>
-      <c r="L634" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="635" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L634"/>
+    </row>
+    <row r="635" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A635" s="2">
         <v>135516100</v>
       </c>
@@ -27128,11 +26868,9 @@
       <c r="K635" s="3" t="s">
         <v>647</v>
       </c>
-      <c r="L635" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="636" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L635"/>
+    </row>
+    <row r="636" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A636" s="2">
         <v>135516250</v>
       </c>
@@ -27166,11 +26904,9 @@
       <c r="K636" s="3" t="s">
         <v>648</v>
       </c>
-      <c r="L636" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="637" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L636"/>
+    </row>
+    <row r="637" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A637" s="2">
         <v>135516445</v>
       </c>
@@ -27204,11 +26940,9 @@
       <c r="K637" s="3" t="s">
         <v>649</v>
       </c>
-      <c r="L637" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="638" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L637"/>
+    </row>
+    <row r="638" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A638" s="2">
         <v>135516937</v>
       </c>
@@ -27242,11 +26976,9 @@
       <c r="K638" s="3" t="s">
         <v>650</v>
       </c>
-      <c r="L638" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="639" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L638"/>
+    </row>
+    <row r="639" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A639" s="2">
         <v>135517023</v>
       </c>
@@ -27280,11 +27012,9 @@
       <c r="K639" s="3" t="s">
         <v>651</v>
       </c>
-      <c r="L639" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="640" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L639"/>
+    </row>
+    <row r="640" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A640" s="2">
         <v>135517068</v>
       </c>
@@ -27318,11 +27048,9 @@
       <c r="K640" s="3" t="s">
         <v>652</v>
       </c>
-      <c r="L640" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="641" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L640"/>
+    </row>
+    <row r="641" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A641" s="2">
         <v>135517144</v>
       </c>
@@ -27356,11 +27084,9 @@
       <c r="K641" s="3" t="s">
         <v>653</v>
       </c>
-      <c r="L641" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="642" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L641"/>
+    </row>
+    <row r="642" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A642" s="2">
         <v>135517674</v>
       </c>
@@ -27394,11 +27120,9 @@
       <c r="K642" s="3" t="s">
         <v>654</v>
       </c>
-      <c r="L642" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="643" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L642"/>
+    </row>
+    <row r="643" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A643" s="2">
         <v>135517944</v>
       </c>
@@ -27432,11 +27156,9 @@
       <c r="K643" s="3" t="s">
         <v>655</v>
       </c>
-      <c r="L643" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="644" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L643"/>
+    </row>
+    <row r="644" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A644" s="2">
         <v>135518265</v>
       </c>
@@ -27470,11 +27192,9 @@
       <c r="K644" s="3" t="s">
         <v>656</v>
       </c>
-      <c r="L644" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="645" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L644"/>
+    </row>
+    <row r="645" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A645" s="2">
         <v>135518267</v>
       </c>
@@ -27508,11 +27228,9 @@
       <c r="K645" s="3" t="s">
         <v>657</v>
       </c>
-      <c r="L645" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="646" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L645"/>
+    </row>
+    <row r="646" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A646" s="2">
         <v>135518531</v>
       </c>
@@ -27546,11 +27264,9 @@
       <c r="K646" s="3" t="s">
         <v>658</v>
       </c>
-      <c r="L646" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="647" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L646"/>
+    </row>
+    <row r="647" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A647" s="2">
         <v>135518797</v>
       </c>
@@ -27584,11 +27300,9 @@
       <c r="K647" s="3" t="s">
         <v>659</v>
       </c>
-      <c r="L647" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="648" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L647"/>
+    </row>
+    <row r="648" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A648" s="2">
         <v>135518987</v>
       </c>
@@ -27622,11 +27336,9 @@
       <c r="K648" s="3" t="s">
         <v>660</v>
       </c>
-      <c r="L648" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="649" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L648"/>
+    </row>
+    <row r="649" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A649" s="2">
         <v>135519029</v>
       </c>
@@ -27660,11 +27372,9 @@
       <c r="K649" s="3" t="s">
         <v>661</v>
       </c>
-      <c r="L649" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="650" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L649"/>
+    </row>
+    <row r="650" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A650" s="2">
         <v>135519254</v>
       </c>
@@ -27698,11 +27408,9 @@
       <c r="K650" s="3" t="s">
         <v>662</v>
       </c>
-      <c r="L650" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="651" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L650"/>
+    </row>
+    <row r="651" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A651" s="2">
         <v>135519591</v>
       </c>
@@ -27736,11 +27444,9 @@
       <c r="K651" s="3" t="s">
         <v>663</v>
       </c>
-      <c r="L651" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="652" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L651"/>
+    </row>
+    <row r="652" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A652" s="2">
         <v>135519605</v>
       </c>
@@ -27774,11 +27480,9 @@
       <c r="K652" s="3" t="s">
         <v>664</v>
       </c>
-      <c r="L652" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="653" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L652"/>
+    </row>
+    <row r="653" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A653" s="2">
         <v>135519874</v>
       </c>
@@ -27812,11 +27516,9 @@
       <c r="K653" s="3" t="s">
         <v>665</v>
       </c>
-      <c r="L653" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="654" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L653"/>
+    </row>
+    <row r="654" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A654" s="2">
         <v>135520365</v>
       </c>
@@ -27850,11 +27552,9 @@
       <c r="K654" s="3" t="s">
         <v>666</v>
       </c>
-      <c r="L654" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="655" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L654"/>
+    </row>
+    <row r="655" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A655" s="2">
         <v>135520381</v>
       </c>
@@ -27888,11 +27588,9 @@
       <c r="K655" s="3" t="s">
         <v>667</v>
       </c>
-      <c r="L655" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="656" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L655"/>
+    </row>
+    <row r="656" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A656" s="2">
         <v>135520573</v>
       </c>
@@ -27926,11 +27624,9 @@
       <c r="K656" s="3" t="s">
         <v>668</v>
       </c>
-      <c r="L656" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="657" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L656"/>
+    </row>
+    <row r="657" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A657" s="2">
         <v>135520838</v>
       </c>
@@ -27964,11 +27660,9 @@
       <c r="K657" s="3" t="s">
         <v>669</v>
       </c>
-      <c r="L657" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="658" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L657"/>
+    </row>
+    <row r="658" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A658" s="2">
         <v>135521036</v>
       </c>
@@ -28002,11 +27696,9 @@
       <c r="K658" s="3" t="s">
         <v>670</v>
       </c>
-      <c r="L658" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="659" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L658"/>
+    </row>
+    <row r="659" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A659" s="2">
         <v>135521097</v>
       </c>
@@ -28040,11 +27732,9 @@
       <c r="K659" s="3" t="s">
         <v>671</v>
       </c>
-      <c r="L659" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="660" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L659"/>
+    </row>
+    <row r="660" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A660" s="2">
         <v>135521414</v>
       </c>
@@ -28078,11 +27768,9 @@
       <c r="K660" s="3" t="s">
         <v>672</v>
       </c>
-      <c r="L660" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="661" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L660"/>
+    </row>
+    <row r="661" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A661" s="2">
         <v>135521504</v>
       </c>
@@ -28116,11 +27804,9 @@
       <c r="K661" s="3" t="s">
         <v>673</v>
       </c>
-      <c r="L661" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="662" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L661"/>
+    </row>
+    <row r="662" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A662" s="2">
         <v>135521535</v>
       </c>
@@ -28154,11 +27840,9 @@
       <c r="K662" s="3" t="s">
         <v>674</v>
       </c>
-      <c r="L662" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="663" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L662"/>
+    </row>
+    <row r="663" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A663" s="2">
         <v>135521542</v>
       </c>
@@ -28192,11 +27876,9 @@
       <c r="K663" s="3" t="s">
         <v>675</v>
       </c>
-      <c r="L663" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="664" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L663"/>
+    </row>
+    <row r="664" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A664" s="2">
         <v>135521562</v>
       </c>
@@ -28230,11 +27912,9 @@
       <c r="K664" s="3" t="s">
         <v>676</v>
       </c>
-      <c r="L664" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="665" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L664"/>
+    </row>
+    <row r="665" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A665" s="2">
         <v>135521623</v>
       </c>
@@ -28268,11 +27948,9 @@
       <c r="K665" s="3" t="s">
         <v>677</v>
       </c>
-      <c r="L665" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="666" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L665"/>
+    </row>
+    <row r="666" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A666" s="2">
         <v>135521668</v>
       </c>
@@ -28306,11 +27984,9 @@
       <c r="K666" s="3" t="s">
         <v>678</v>
       </c>
-      <c r="L666" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="667" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L666"/>
+    </row>
+    <row r="667" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A667" s="2">
         <v>135521812</v>
       </c>
@@ -28344,11 +28020,9 @@
       <c r="K667" s="3" t="s">
         <v>679</v>
       </c>
-      <c r="L667" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="668" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L667"/>
+    </row>
+    <row r="668" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A668" s="2">
         <v>135521825</v>
       </c>
@@ -28382,11 +28056,9 @@
       <c r="K668" s="3" t="s">
         <v>680</v>
       </c>
-      <c r="L668" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="669" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L668"/>
+    </row>
+    <row r="669" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A669" s="2">
         <v>135522094</v>
       </c>
@@ -28420,11 +28092,9 @@
       <c r="K669" s="3" t="s">
         <v>681</v>
       </c>
-      <c r="L669" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="670" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L669"/>
+    </row>
+    <row r="670" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A670" s="2">
         <v>135522692</v>
       </c>
@@ -28458,11 +28128,9 @@
       <c r="K670" s="3" t="s">
         <v>682</v>
       </c>
-      <c r="L670" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="671" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L670"/>
+    </row>
+    <row r="671" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A671" s="2">
         <v>135522851</v>
       </c>
@@ -28496,11 +28164,9 @@
       <c r="K671" s="3" t="s">
         <v>683</v>
       </c>
-      <c r="L671" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="672" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L671"/>
+    </row>
+    <row r="672" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A672" s="2">
         <v>135523294</v>
       </c>
@@ -28534,11 +28200,9 @@
       <c r="K672" s="3" t="s">
         <v>684</v>
       </c>
-      <c r="L672" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="673" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L672"/>
+    </row>
+    <row r="673" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A673" s="2">
         <v>135523673</v>
       </c>
@@ -28572,11 +28236,9 @@
       <c r="K673" s="3" t="s">
         <v>685</v>
       </c>
-      <c r="L673" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="674" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L673"/>
+    </row>
+    <row r="674" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A674" s="2">
         <v>135523707</v>
       </c>
@@ -28610,11 +28272,9 @@
       <c r="K674" s="3" t="s">
         <v>686</v>
       </c>
-      <c r="L674" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="675" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L674"/>
+    </row>
+    <row r="675" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A675" s="2">
         <v>135523792</v>
       </c>
@@ -28648,11 +28308,9 @@
       <c r="K675" s="3" t="s">
         <v>687</v>
       </c>
-      <c r="L675" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="676" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L675"/>
+    </row>
+    <row r="676" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A676" s="2">
         <v>135523916</v>
       </c>
@@ -28686,11 +28344,9 @@
       <c r="K676" s="3" t="s">
         <v>688</v>
       </c>
-      <c r="L676" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="677" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L676"/>
+    </row>
+    <row r="677" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A677" s="2">
         <v>135524544</v>
       </c>
@@ -28724,11 +28380,9 @@
       <c r="K677" s="3" t="s">
         <v>689</v>
       </c>
-      <c r="L677" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="678" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L677"/>
+    </row>
+    <row r="678" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A678" s="2">
         <v>135524548</v>
       </c>
@@ -28762,11 +28416,9 @@
       <c r="K678" s="3" t="s">
         <v>690</v>
       </c>
-      <c r="L678" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="679" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L678"/>
+    </row>
+    <row r="679" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A679" s="2">
         <v>135524860</v>
       </c>
@@ -28800,11 +28452,9 @@
       <c r="K679" s="3" t="s">
         <v>691</v>
       </c>
-      <c r="L679" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="680" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L679"/>
+    </row>
+    <row r="680" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A680" s="2">
         <v>135524988</v>
       </c>
@@ -28838,11 +28488,9 @@
       <c r="K680" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="L680" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="681" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L680"/>
+    </row>
+    <row r="681" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A681" s="2">
         <v>135525285</v>
       </c>
@@ -28876,11 +28524,9 @@
       <c r="K681" s="3" t="s">
         <v>693</v>
       </c>
-      <c r="L681" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="682" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L681"/>
+    </row>
+    <row r="682" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A682" s="2">
         <v>135525374</v>
       </c>
@@ -28914,11 +28560,9 @@
       <c r="K682" s="3" t="s">
         <v>694</v>
       </c>
-      <c r="L682" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="683" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L682"/>
+    </row>
+    <row r="683" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A683" s="2">
         <v>135525414</v>
       </c>
@@ -28952,11 +28596,9 @@
       <c r="K683" s="3" t="s">
         <v>695</v>
       </c>
-      <c r="L683" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="684" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L683"/>
+    </row>
+    <row r="684" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A684" s="2">
         <v>135525723</v>
       </c>
@@ -28990,11 +28632,9 @@
       <c r="K684" s="3" t="s">
         <v>696</v>
       </c>
-      <c r="L684" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="685" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L684"/>
+    </row>
+    <row r="685" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A685" s="2">
         <v>135525889</v>
       </c>
@@ -29028,11 +28668,9 @@
       <c r="K685" s="3" t="s">
         <v>697</v>
       </c>
-      <c r="L685" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="686" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L685"/>
+    </row>
+    <row r="686" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A686" s="2">
         <v>135526223</v>
       </c>
@@ -29066,11 +28704,9 @@
       <c r="K686" s="3" t="s">
         <v>698</v>
       </c>
-      <c r="L686" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="687" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L686"/>
+    </row>
+    <row r="687" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A687" s="2">
         <v>135528883</v>
       </c>
@@ -29104,11 +28740,9 @@
       <c r="K687" s="3" t="s">
         <v>699</v>
       </c>
-      <c r="L687" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="688" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L687"/>
+    </row>
+    <row r="688" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A688" s="2">
         <v>135528959</v>
       </c>
@@ -29142,11 +28776,9 @@
       <c r="K688" s="3" t="s">
         <v>700</v>
       </c>
-      <c r="L688" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="689" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L688"/>
+    </row>
+    <row r="689" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A689" s="2">
         <v>135530566</v>
       </c>
@@ -29180,11 +28812,9 @@
       <c r="K689" s="3" t="s">
         <v>701</v>
       </c>
-      <c r="L689" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="690" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L689"/>
+    </row>
+    <row r="690" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A690" s="2">
         <v>135530574</v>
       </c>
@@ -29218,11 +28848,9 @@
       <c r="K690" s="3" t="s">
         <v>702</v>
       </c>
-      <c r="L690" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="691" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L690"/>
+    </row>
+    <row r="691" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A691" s="2">
         <v>135531524</v>
       </c>
@@ -29256,11 +28884,9 @@
       <c r="K691" s="3" t="s">
         <v>703</v>
       </c>
-      <c r="L691" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="692" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L691"/>
+    </row>
+    <row r="692" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A692" s="2">
         <v>135534438</v>
       </c>
@@ -29294,11 +28920,9 @@
       <c r="K692" s="3" t="s">
         <v>704</v>
       </c>
-      <c r="L692" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="693" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L692"/>
+    </row>
+    <row r="693" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A693" s="2">
         <v>135534662</v>
       </c>
@@ -29332,11 +28956,9 @@
       <c r="K693" s="3" t="s">
         <v>705</v>
       </c>
-      <c r="L693" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="694" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L693"/>
+    </row>
+    <row r="694" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A694" s="2">
         <v>135535078</v>
       </c>
@@ -29370,11 +28992,9 @@
       <c r="K694" s="3" t="s">
         <v>706</v>
       </c>
-      <c r="L694" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="695" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L694"/>
+    </row>
+    <row r="695" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A695" s="2">
         <v>135535592</v>
       </c>
@@ -29408,11 +29028,9 @@
       <c r="K695" s="3" t="s">
         <v>707</v>
       </c>
-      <c r="L695" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="696" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L695"/>
+    </row>
+    <row r="696" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A696" s="2">
         <v>135535750</v>
       </c>
@@ -29446,11 +29064,9 @@
       <c r="K696" s="3" t="s">
         <v>708</v>
       </c>
-      <c r="L696" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="697" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L696"/>
+    </row>
+    <row r="697" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A697" s="2">
         <v>135536207</v>
       </c>
@@ -29484,11 +29100,9 @@
       <c r="K697" s="3" t="s">
         <v>709</v>
       </c>
-      <c r="L697" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="698" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L697"/>
+    </row>
+    <row r="698" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A698" s="2">
         <v>135536270</v>
       </c>
@@ -29522,11 +29136,9 @@
       <c r="K698" s="3" t="s">
         <v>710</v>
       </c>
-      <c r="L698" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="699" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L698"/>
+    </row>
+    <row r="699" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A699" s="2">
         <v>135537819</v>
       </c>
@@ -29560,11 +29172,9 @@
       <c r="K699" s="3" t="s">
         <v>711</v>
       </c>
-      <c r="L699" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="700" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L699"/>
+    </row>
+    <row r="700" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A700" s="2">
         <v>135540080</v>
       </c>
@@ -29598,11 +29208,9 @@
       <c r="K700" s="3" t="s">
         <v>712</v>
       </c>
-      <c r="L700" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="701" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L700"/>
+    </row>
+    <row r="701" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A701" s="2">
         <v>135541132</v>
       </c>
@@ -29636,11 +29244,9 @@
       <c r="K701" s="3" t="s">
         <v>713</v>
       </c>
-      <c r="L701" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="702" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L701"/>
+    </row>
+    <row r="702" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A702" s="2">
         <v>135542716</v>
       </c>
@@ -29674,11 +29280,9 @@
       <c r="K702" s="3" t="s">
         <v>714</v>
       </c>
-      <c r="L702" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="703" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L702"/>
+    </row>
+    <row r="703" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A703" s="2">
         <v>135543767</v>
       </c>
@@ -29712,11 +29316,9 @@
       <c r="K703" s="3" t="s">
         <v>715</v>
       </c>
-      <c r="L703" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="704" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L703"/>
+    </row>
+    <row r="704" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A704" s="2">
         <v>135544220</v>
       </c>
@@ -29750,11 +29352,9 @@
       <c r="K704" s="3" t="s">
         <v>716</v>
       </c>
-      <c r="L704" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="705" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L704"/>
+    </row>
+    <row r="705" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A705" s="2">
         <v>135544398</v>
       </c>
@@ -29788,11 +29388,9 @@
       <c r="K705" s="3" t="s">
         <v>717</v>
       </c>
-      <c r="L705" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="706" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L705"/>
+    </row>
+    <row r="706" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A706" s="2">
         <v>135545740</v>
       </c>
@@ -29826,11 +29424,9 @@
       <c r="K706" s="3" t="s">
         <v>718</v>
       </c>
-      <c r="L706" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="707" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L706"/>
+    </row>
+    <row r="707" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A707" s="2">
         <v>135545974</v>
       </c>
@@ -29864,11 +29460,9 @@
       <c r="K707" s="3" t="s">
         <v>719</v>
       </c>
-      <c r="L707" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="708" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L707"/>
+    </row>
+    <row r="708" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A708" s="2">
         <v>135547182</v>
       </c>
@@ -29902,11 +29496,9 @@
       <c r="K708" s="3" t="s">
         <v>720</v>
       </c>
-      <c r="L708" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="709" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L708"/>
+    </row>
+    <row r="709" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A709" s="2">
         <v>135548004</v>
       </c>
@@ -29940,9 +29532,7 @@
       <c r="K709" s="3" t="s">
         <v>721</v>
       </c>
-      <c r="L709" t="s">
-        <v>734</v>
-      </c>
+      <c r="L709"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:M135" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -29951,73 +29541,73 @@
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule dxfId="0" priority="71" type="duplicateValues"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="71"/>
   </conditionalFormatting>
-  <pageMargins bottom="0.78740157499999996" footer="0.31496062000000002" header="0.31496062000000002" left="0.511811024" right="0.511811024" top="0.78740157499999996"/>
-  <pageSetup orientation="portrait" paperSize="9" r:id="rId1"/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter>
-    <oddFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FPÚBLICO]]></oddFooter>
-    <evenFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FPÚBLICO]]></evenFooter>
-    <firstFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FPÚBLICO]]></firstFooter>
+    <oddFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FPÚBLICO</oddFooter>
+    <evenFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FPÚBLICO</evenFooter>
+    <firstFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FPÚBLICO</firstFooter>
   </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3317CFC-26C3-4764-9E25-62442657C783}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3317CFC-26C3-4764-9E25-62442657C783}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
-  <pageMargins bottom="0.78740157499999996" footer="0.31496062000000002" header="0.31496062000000002" left="0.511811024" right="0.511811024" top="0.78740157499999996"/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Planilha3">
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
-  <pageMargins bottom="0.78740157499999996" footer="0.31496062000000002" header="0.31496062000000002" left="0.511811024" right="0.511811024" top="0.78740157499999996"/>
-  <pageSetup orientation="portrait" paperSize="9" r:id="rId1"/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter>
-    <oddFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FPÚBLICO]]></oddFooter>
-    <evenFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FPÚBLICO]]></evenFooter>
-    <firstFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FPÚBLICO]]></firstFooter>
+    <oddFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FPÚBLICO</oddFooter>
+    <evenFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FPÚBLICO</evenFooter>
+    <firstFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FPÚBLICO</firstFooter>
   </headerFooter>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
+  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTAxOTQ2PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MjgvMDUvMjAxOSAxNzoxNTowNTwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAyOC8wNS8yMDE5ICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
-  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB274C4F-D882-4147-9885-1FF717648542}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DCA74A62-E908-4C3E-A1D4-6DC1121C84E7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB274C4F-D882-4147-9885-1FF717648542}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>